--- a/research/traditional_assets/database/data/thailand/thailand_information_services.xlsx
+++ b/research/traditional_assets/database/data/thailand/thailand_information_services.xlsx
@@ -1397,7 +1397,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1534,22 +1534,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1116791261068374</v>
+        <v>0.1114917678546238</v>
       </c>
       <c r="C2">
-        <v>5.725973076931526</v>
+        <v>5.674890607896042</v>
       </c>
       <c r="D2">
-        <v>2.165973076931526</v>
+        <v>2.172150607896043</v>
       </c>
       <c r="E2">
-        <v>-0.066</v>
+        <v>-0.008740000000000005</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.05726</v>
       </c>
       <c r="G2">
         <v>3.56</v>
@@ -1570,28 +1570,28 @@
         <v>0.488</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.002880178</v>
       </c>
       <c r="N2">
-        <v>0.488</v>
+        <v>0.485119822</v>
       </c>
       <c r="O2">
-        <v>0.09760000000000001</v>
+        <v>0.0970239644</v>
       </c>
       <c r="P2">
-        <v>0.3904</v>
+        <v>0.3880958576</v>
       </c>
       <c r="Q2">
-        <v>0.4763999999999999</v>
+        <v>0.4740958575999999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1116791261068374</v>
+        <v>0.1122114826814382</v>
       </c>
       <c r="T2">
-        <v>1.01912912879999</v>
+        <v>1.027364515699383</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>169.4339724836451</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1616,22 +1616,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1114917678546238</v>
+        <v>0.1113044096024101</v>
       </c>
       <c r="C3">
-        <v>5.674890607896042</v>
+        <v>5.623843477287743</v>
       </c>
       <c r="D3">
-        <v>2.172150607896043</v>
+        <v>2.178363477287743</v>
       </c>
       <c r="E3">
-        <v>-0.008740000000000005</v>
+        <v>0.04851999999999999</v>
       </c>
       <c r="F3">
-        <v>0.05726</v>
+        <v>0.11452</v>
       </c>
       <c r="G3">
         <v>3.56</v>
@@ -1652,28 +1652,28 @@
         <v>0.488</v>
       </c>
       <c r="M3">
-        <v>0.002880178</v>
+        <v>0.005760355999999999</v>
       </c>
       <c r="N3">
-        <v>0.485119822</v>
+        <v>0.482239644</v>
       </c>
       <c r="O3">
-        <v>0.0970239644</v>
+        <v>0.0964479288</v>
       </c>
       <c r="P3">
-        <v>0.3880958576</v>
+        <v>0.3857917152</v>
       </c>
       <c r="Q3">
-        <v>0.4740958575999999</v>
+        <v>0.4717917152</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1122114826814382</v>
+        <v>0.1127547036759287</v>
       </c>
       <c r="T3">
-        <v>1.027364515699383</v>
+        <v>1.035767971719173</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>169.4339724836451</v>
+        <v>84.71698624182255</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1698,22 +1698,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1113044096024101</v>
+        <v>0.1111170513501964</v>
       </c>
       <c r="C4">
-        <v>5.623843477287743</v>
+        <v>5.572831989205443</v>
       </c>
       <c r="D4">
-        <v>2.178363477287743</v>
+        <v>2.184611989205443</v>
       </c>
       <c r="E4">
-        <v>0.04851999999999999</v>
+        <v>0.10578</v>
       </c>
       <c r="F4">
-        <v>0.11452</v>
+        <v>0.17178</v>
       </c>
       <c r="G4">
         <v>3.56</v>
@@ -1734,28 +1734,28 @@
         <v>0.488</v>
       </c>
       <c r="M4">
-        <v>0.005760355999999999</v>
+        <v>0.008640533999999998</v>
       </c>
       <c r="N4">
-        <v>0.482239644</v>
+        <v>0.479359466</v>
       </c>
       <c r="O4">
-        <v>0.0964479288</v>
+        <v>0.0958718932</v>
       </c>
       <c r="P4">
-        <v>0.3857917152</v>
+        <v>0.3834875728</v>
       </c>
       <c r="Q4">
-        <v>0.4717917152</v>
+        <v>0.4694875728</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1127547036759287</v>
+        <v>0.1133091251032953</v>
       </c>
       <c r="T4">
-        <v>1.035767971719173</v>
+        <v>1.044344694873391</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>84.71698624182255</v>
+        <v>56.47799082788171</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1780,22 +1780,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1111170513501964</v>
+        <v>0.1109296930979828</v>
       </c>
       <c r="C5">
-        <v>5.572831989205443</v>
+        <v>5.521856451247154</v>
       </c>
       <c r="D5">
-        <v>2.184611989205443</v>
+        <v>2.190896451247154</v>
       </c>
       <c r="E5">
-        <v>0.10578</v>
+        <v>0.16304</v>
       </c>
       <c r="F5">
-        <v>0.17178</v>
+        <v>0.22904</v>
       </c>
       <c r="G5">
         <v>3.56</v>
@@ -1816,28 +1816,28 @@
         <v>0.488</v>
       </c>
       <c r="M5">
-        <v>0.008640533999999998</v>
+        <v>0.011520712</v>
       </c>
       <c r="N5">
-        <v>0.479359466</v>
+        <v>0.476479288</v>
       </c>
       <c r="O5">
-        <v>0.0958718932</v>
+        <v>0.09529585760000001</v>
       </c>
       <c r="P5">
-        <v>0.3834875728</v>
+        <v>0.3811834304</v>
       </c>
       <c r="Q5">
-        <v>0.4694875728</v>
+        <v>0.4671834304</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1133091251032953</v>
+        <v>0.1138750969770654</v>
       </c>
       <c r="T5">
-        <v>1.044344694873391</v>
+        <v>1.053100099759989</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>56.47799082788171</v>
+        <v>42.35849312091128</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1862,22 +1862,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1109296930979828</v>
+        <v>0.1107423348457691</v>
       </c>
       <c r="C6">
-        <v>5.521856451247154</v>
+        <v>5.470917174560563</v>
       </c>
       <c r="D6">
-        <v>2.190896451247154</v>
+        <v>2.197217174560563</v>
       </c>
       <c r="E6">
-        <v>0.16304</v>
+        <v>0.2203</v>
       </c>
       <c r="F6">
-        <v>0.22904</v>
+        <v>0.2863</v>
       </c>
       <c r="G6">
         <v>3.56</v>
@@ -1898,28 +1898,28 @@
         <v>0.488</v>
       </c>
       <c r="M6">
-        <v>0.011520712</v>
+        <v>0.01440089</v>
       </c>
       <c r="N6">
-        <v>0.476479288</v>
+        <v>0.47359911</v>
       </c>
       <c r="O6">
-        <v>0.09529585760000001</v>
+        <v>0.09471982200000001</v>
       </c>
       <c r="P6">
-        <v>0.3811834304</v>
+        <v>0.378879288</v>
       </c>
       <c r="Q6">
-        <v>0.4671834304</v>
+        <v>0.4648792879999999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1138750969770654</v>
+        <v>0.114452984048178</v>
       </c>
       <c r="T6">
-        <v>1.053100099759989</v>
+        <v>1.062039828959989</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>42.35849312091128</v>
+        <v>33.88679449672902</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1944,22 +1944,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1107423348457691</v>
+        <v>0.1105549765935554</v>
       </c>
       <c r="C7">
-        <v>5.470917174560563</v>
+        <v>5.42001447389438</v>
       </c>
       <c r="D7">
-        <v>2.197217174560563</v>
+        <v>2.203574473894379</v>
       </c>
       <c r="E7">
-        <v>0.2203</v>
+        <v>0.27756</v>
       </c>
       <c r="F7">
-        <v>0.2863</v>
+        <v>0.34356</v>
       </c>
       <c r="G7">
         <v>3.56</v>
@@ -1980,28 +1980,28 @@
         <v>0.488</v>
       </c>
       <c r="M7">
-        <v>0.01440089</v>
+        <v>0.017281068</v>
       </c>
       <c r="N7">
-        <v>0.47359911</v>
+        <v>0.470718932</v>
       </c>
       <c r="O7">
-        <v>0.09471982200000001</v>
+        <v>0.0941437864</v>
       </c>
       <c r="P7">
-        <v>0.378879288</v>
+        <v>0.3765751456</v>
       </c>
       <c r="Q7">
-        <v>0.4648792879999999</v>
+        <v>0.4625751456</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.114452984048178</v>
+        <v>0.1150431665888887</v>
       </c>
       <c r="T7">
-        <v>1.062039828959989</v>
+        <v>1.071169765164244</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>33.88679449672902</v>
+        <v>28.23899541394085</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2026,22 +2026,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1105549765935554</v>
+        <v>0.1103676183413417</v>
       </c>
       <c r="C8">
-        <v>5.42001447389438</v>
+        <v>5.369148667650588</v>
       </c>
       <c r="D8">
-        <v>2.203574473894379</v>
+        <v>2.209968667650588</v>
       </c>
       <c r="E8">
-        <v>0.27756</v>
+        <v>0.33482</v>
       </c>
       <c r="F8">
-        <v>0.34356</v>
+        <v>0.40082</v>
       </c>
       <c r="G8">
         <v>3.56</v>
@@ -2062,28 +2062,28 @@
         <v>0.488</v>
       </c>
       <c r="M8">
-        <v>0.017281068</v>
+        <v>0.020161246</v>
       </c>
       <c r="N8">
-        <v>0.470718932</v>
+        <v>0.467838754</v>
       </c>
       <c r="O8">
-        <v>0.0941437864</v>
+        <v>0.0935677508</v>
       </c>
       <c r="P8">
-        <v>0.3765751456</v>
+        <v>0.3742710032</v>
       </c>
       <c r="Q8">
-        <v>0.4625751456</v>
+        <v>0.4602710031999999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1150431665888887</v>
+        <v>0.1156460412272492</v>
       </c>
       <c r="T8">
-        <v>1.071169765164244</v>
+        <v>1.08049604408257</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>28.23899541394086</v>
+        <v>24.2048532119493</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2108,22 +2108,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1103676183413417</v>
+        <v>0.1101802600891281</v>
       </c>
       <c r="C9">
-        <v>5.369148667650588</v>
+        <v>5.318320077937606</v>
       </c>
       <c r="D9">
-        <v>2.209968667650589</v>
+        <v>2.216400077937605</v>
       </c>
       <c r="E9">
-        <v>0.33482</v>
+        <v>0.39208</v>
       </c>
       <c r="F9">
-        <v>0.40082</v>
+        <v>0.45808</v>
       </c>
       <c r="G9">
         <v>3.56</v>
@@ -2144,28 +2144,28 @@
         <v>0.488</v>
       </c>
       <c r="M9">
-        <v>0.020161246</v>
+        <v>0.023041424</v>
       </c>
       <c r="N9">
-        <v>0.467838754</v>
+        <v>0.464958576</v>
       </c>
       <c r="O9">
-        <v>0.0935677508</v>
+        <v>0.09299171520000001</v>
       </c>
       <c r="P9">
-        <v>0.3742710032</v>
+        <v>0.3719668608</v>
       </c>
       <c r="Q9">
-        <v>0.4602710031999999</v>
+        <v>0.4579668608</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1156460412272492</v>
+        <v>0.1162620218360088</v>
       </c>
       <c r="T9">
-        <v>1.08049604408257</v>
+        <v>1.090025068194771</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2182,7 +2182,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>24.2048532119493</v>
+        <v>21.17924656045564</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2190,22 +2190,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1101802600891281</v>
+        <v>0.1099929018369144</v>
       </c>
       <c r="C10">
-        <v>5.318320077937606</v>
+        <v>5.267529030624361</v>
       </c>
       <c r="D10">
-        <v>2.216400077937605</v>
+        <v>2.222869030624361</v>
       </c>
       <c r="E10">
-        <v>0.39208</v>
+        <v>0.44934</v>
       </c>
       <c r="F10">
-        <v>0.45808</v>
+        <v>0.51534</v>
       </c>
       <c r="G10">
         <v>3.56</v>
@@ -2226,28 +2226,28 @@
         <v>0.488</v>
       </c>
       <c r="M10">
-        <v>0.023041424</v>
+        <v>0.025921602</v>
       </c>
       <c r="N10">
-        <v>0.464958576</v>
+        <v>0.462078398</v>
       </c>
       <c r="O10">
-        <v>0.09299171520000001</v>
+        <v>0.09241567960000001</v>
       </c>
       <c r="P10">
-        <v>0.3719668608</v>
+        <v>0.3696627184</v>
       </c>
       <c r="Q10">
-        <v>0.4579668608</v>
+        <v>0.4556627183999999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1162620218360088</v>
+        <v>0.1168915404801257</v>
       </c>
       <c r="T10">
-        <v>1.090025068194771</v>
+        <v>1.09976352140834</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>21.17924656045564</v>
+        <v>18.82599694262723</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2272,22 +2272,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1099929018369144</v>
+        <v>0.1098055435847007</v>
       </c>
       <c r="C11">
-        <v>5.267529030624361</v>
+        <v>5.216775855395355</v>
       </c>
       <c r="D11">
-        <v>2.222869030624361</v>
+        <v>2.229375855395354</v>
       </c>
       <c r="E11">
-        <v>0.44934</v>
+        <v>0.5065999999999999</v>
       </c>
       <c r="F11">
-        <v>0.51534</v>
+        <v>0.5726</v>
       </c>
       <c r="G11">
         <v>3.56</v>
@@ -2308,28 +2308,28 @@
         <v>0.488</v>
       </c>
       <c r="M11">
-        <v>0.025921602</v>
+        <v>0.02880178</v>
       </c>
       <c r="N11">
-        <v>0.462078398</v>
+        <v>0.45919822</v>
       </c>
       <c r="O11">
-        <v>0.09241567960000001</v>
+        <v>0.091839644</v>
       </c>
       <c r="P11">
-        <v>0.3696627184</v>
+        <v>0.367358576</v>
       </c>
       <c r="Q11">
-        <v>0.4556627183999999</v>
+        <v>0.453358576</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1168915404801257</v>
+        <v>0.1175350484274452</v>
       </c>
       <c r="T11">
-        <v>1.09976352140834</v>
+        <v>1.109718384693322</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>18.82599694262723</v>
+        <v>16.94339724836451</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2354,22 +2354,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1098055435847007</v>
+        <v>0.109618185332487</v>
       </c>
       <c r="C12">
-        <v>5.216775855395353</v>
+        <v>5.166060885806639</v>
       </c>
       <c r="D12">
-        <v>2.229375855395353</v>
+        <v>2.23592088580664</v>
       </c>
       <c r="E12">
-        <v>0.5065999999999999</v>
+        <v>0.56386</v>
       </c>
       <c r="F12">
-        <v>0.5726</v>
+        <v>0.62986</v>
       </c>
       <c r="G12">
         <v>3.56</v>
@@ -2390,28 +2390,28 @@
         <v>0.488</v>
       </c>
       <c r="M12">
-        <v>0.02880178</v>
+        <v>0.031681958</v>
       </c>
       <c r="N12">
-        <v>0.45919822</v>
+        <v>0.456318042</v>
       </c>
       <c r="O12">
-        <v>0.091839644</v>
+        <v>0.0912636084</v>
       </c>
       <c r="P12">
-        <v>0.367358576</v>
+        <v>0.3650544336</v>
       </c>
       <c r="Q12">
-        <v>0.453358576</v>
+        <v>0.4510544336</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1175350484274452</v>
+        <v>0.1181930172275135</v>
       </c>
       <c r="T12">
-        <v>1.109718384693322</v>
+        <v>1.119896952771224</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>16.94339724836451</v>
+        <v>15.4030884076041</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2436,22 +2436,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.109618185332487</v>
+        <v>0.1094308270802734</v>
       </c>
       <c r="C13">
-        <v>5.166060885806639</v>
+        <v>5.115384459342849</v>
       </c>
       <c r="D13">
-        <v>2.23592088580664</v>
+        <v>2.242504459342849</v>
       </c>
       <c r="E13">
-        <v>0.56386</v>
+        <v>0.6211199999999999</v>
       </c>
       <c r="F13">
-        <v>0.62986</v>
+        <v>0.68712</v>
       </c>
       <c r="G13">
         <v>3.56</v>
@@ -2472,28 +2472,28 @@
         <v>0.488</v>
       </c>
       <c r="M13">
-        <v>0.031681958</v>
+        <v>0.03456213599999999</v>
       </c>
       <c r="N13">
-        <v>0.456318042</v>
+        <v>0.453437864</v>
       </c>
       <c r="O13">
-        <v>0.0912636084</v>
+        <v>0.0906875728</v>
       </c>
       <c r="P13">
-        <v>0.3650544336</v>
+        <v>0.3627502912</v>
       </c>
       <c r="Q13">
-        <v>0.4510544336</v>
+        <v>0.4487502911999999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1181930172275135</v>
+        <v>0.118865939863947</v>
       </c>
       <c r="T13">
-        <v>1.119896952771224</v>
+        <v>1.130306851941807</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>15.4030884076041</v>
+        <v>14.11949770697043</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2518,22 +2518,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1094308270802734</v>
+        <v>0.1092434688280597</v>
       </c>
       <c r="C14">
-        <v>5.115384459342849</v>
+        <v>5.064746917475183</v>
       </c>
       <c r="D14">
-        <v>2.242504459342849</v>
+        <v>2.249126917475183</v>
       </c>
       <c r="E14">
-        <v>0.6211199999999999</v>
+        <v>0.67838</v>
       </c>
       <c r="F14">
-        <v>0.68712</v>
+        <v>0.74438</v>
       </c>
       <c r="G14">
         <v>3.56</v>
@@ -2554,28 +2554,28 @@
         <v>0.488</v>
       </c>
       <c r="M14">
-        <v>0.03456213599999999</v>
+        <v>0.037442314</v>
       </c>
       <c r="N14">
-        <v>0.453437864</v>
+        <v>0.450557686</v>
       </c>
       <c r="O14">
-        <v>0.0906875728</v>
+        <v>0.09011153720000001</v>
       </c>
       <c r="P14">
-        <v>0.3627502912</v>
+        <v>0.3604461488</v>
       </c>
       <c r="Q14">
-        <v>0.4487502911999999</v>
+        <v>0.4464461488</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.118865939863947</v>
+        <v>0.1195543319862755</v>
       </c>
       <c r="T14">
-        <v>1.130306851941807</v>
+        <v>1.140956059139299</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2592,7 +2592,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>14.11949770697043</v>
+        <v>13.03338249874193</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2600,22 +2600,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1092434688280597</v>
+        <v>0.109224110575846</v>
       </c>
       <c r="C15">
-        <v>5.064746917475183</v>
+        <v>5.008173394049055</v>
       </c>
       <c r="D15">
-        <v>2.249126917475183</v>
+        <v>2.249813394049055</v>
       </c>
       <c r="E15">
-        <v>0.67838</v>
+        <v>0.7356400000000001</v>
       </c>
       <c r="F15">
-        <v>0.74438</v>
+        <v>0.80164</v>
       </c>
       <c r="G15">
         <v>3.56</v>
@@ -2636,45 +2636,45 @@
         <v>0.488</v>
       </c>
       <c r="M15">
-        <v>0.037442314</v>
+        <v>0.041524952</v>
       </c>
       <c r="N15">
-        <v>0.450557686</v>
+        <v>0.446475048</v>
       </c>
       <c r="O15">
-        <v>0.09011153720000001</v>
+        <v>0.0892950096</v>
       </c>
       <c r="P15">
-        <v>0.3604461488</v>
+        <v>0.3571800384</v>
       </c>
       <c r="Q15">
-        <v>0.4464461488</v>
+        <v>0.4431800384</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1195543319862755</v>
+        <v>0.1202587332277279</v>
       </c>
       <c r="T15">
-        <v>1.140956059139299</v>
+        <v>1.151852922318128</v>
       </c>
       <c r="U15">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V15">
         <v>0.2</v>
       </c>
       <c r="W15">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>13.03338249874193</v>
+        <v>11.75197023707577</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2682,22 +2682,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.109224110575846</v>
+        <v>0.1090487523236323</v>
       </c>
       <c r="C16">
-        <v>5.008173394049055</v>
+        <v>4.957151040328126</v>
       </c>
       <c r="D16">
-        <v>2.249813394049055</v>
+        <v>2.256051040328126</v>
       </c>
       <c r="E16">
-        <v>0.7356400000000001</v>
+        <v>0.7929000000000002</v>
       </c>
       <c r="F16">
-        <v>0.80164</v>
+        <v>0.8589000000000001</v>
       </c>
       <c r="G16">
         <v>3.56</v>
@@ -2718,28 +2718,28 @@
         <v>0.488</v>
       </c>
       <c r="M16">
-        <v>0.041524952</v>
+        <v>0.04449102000000001</v>
       </c>
       <c r="N16">
-        <v>0.446475048</v>
+        <v>0.44350898</v>
       </c>
       <c r="O16">
-        <v>0.0892950096</v>
+        <v>0.088701796</v>
       </c>
       <c r="P16">
-        <v>0.3571800384</v>
+        <v>0.354807184</v>
       </c>
       <c r="Q16">
-        <v>0.4431800384</v>
+        <v>0.440807184</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1202587332277279</v>
+        <v>0.120979708616038</v>
       </c>
       <c r="T16">
-        <v>1.151852922318128</v>
+        <v>1.163006182277635</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2756,7 +2756,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.75197023707577</v>
+        <v>10.96850555460405</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2764,22 +2764,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1090487523236323</v>
+        <v>0.1088733940714186</v>
       </c>
       <c r="C17">
-        <v>4.957151040328126</v>
+        <v>4.906163370732431</v>
       </c>
       <c r="D17">
-        <v>2.256051040328126</v>
+        <v>2.262323370732431</v>
       </c>
       <c r="E17">
-        <v>0.7928999999999999</v>
+        <v>0.85016</v>
       </c>
       <c r="F17">
-        <v>0.8589</v>
+        <v>0.91616</v>
       </c>
       <c r="G17">
         <v>3.56</v>
@@ -2800,28 +2800,28 @@
         <v>0.488</v>
       </c>
       <c r="M17">
-        <v>0.04449102</v>
+        <v>0.04745708799999999</v>
       </c>
       <c r="N17">
-        <v>0.44350898</v>
+        <v>0.440542912</v>
       </c>
       <c r="O17">
-        <v>0.088701796</v>
+        <v>0.08810858240000001</v>
       </c>
       <c r="P17">
-        <v>0.354807184</v>
+        <v>0.3524343296</v>
       </c>
       <c r="Q17">
-        <v>0.440807184</v>
+        <v>0.4384343296</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.120979708616038</v>
+        <v>0.1217178500850222</v>
       </c>
       <c r="T17">
-        <v>1.163006182277635</v>
+        <v>1.174424996045702</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2838,7 +2838,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>10.96850555460405</v>
+        <v>10.2829739574413</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2846,22 +2846,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1088733940714186</v>
+        <v>0.108929235819205</v>
       </c>
       <c r="C18">
-        <v>4.906163370732431</v>
+        <v>4.84690220456211</v>
       </c>
       <c r="D18">
-        <v>2.262323370732431</v>
+        <v>2.260322204562109</v>
       </c>
       <c r="E18">
-        <v>0.85016</v>
+        <v>0.9074200000000001</v>
       </c>
       <c r="F18">
-        <v>0.91616</v>
+        <v>0.9734200000000001</v>
       </c>
       <c r="G18">
         <v>3.56</v>
@@ -2882,45 +2882,45 @@
         <v>0.488</v>
       </c>
       <c r="M18">
-        <v>0.04745708799999999</v>
+        <v>0.05207797</v>
       </c>
       <c r="N18">
-        <v>0.440542912</v>
+        <v>0.43592203</v>
       </c>
       <c r="O18">
-        <v>0.08810858240000001</v>
+        <v>0.08718440599999999</v>
       </c>
       <c r="P18">
-        <v>0.3524343296</v>
+        <v>0.348737624</v>
       </c>
       <c r="Q18">
-        <v>0.4384343296</v>
+        <v>0.4347376239999999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1217178500850222</v>
+        <v>0.1224737780954277</v>
       </c>
       <c r="T18">
-        <v>1.174424996045702</v>
+        <v>1.186118961952759</v>
       </c>
       <c r="U18">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V18">
         <v>0.2</v>
       </c>
       <c r="W18">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>10.2829739574413</v>
+        <v>9.3705649432956</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2928,22 +2928,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.108929235819205</v>
+        <v>0.1087674775669913</v>
       </c>
       <c r="C19">
-        <v>4.84690220456211</v>
+        <v>4.795448785727135</v>
       </c>
       <c r="D19">
-        <v>2.260322204562109</v>
+        <v>2.266128785727135</v>
       </c>
       <c r="E19">
-        <v>0.9074200000000001</v>
+        <v>0.96468</v>
       </c>
       <c r="F19">
-        <v>0.9734200000000001</v>
+        <v>1.03068</v>
       </c>
       <c r="G19">
         <v>3.56</v>
@@ -2964,28 +2964,28 @@
         <v>0.488</v>
       </c>
       <c r="M19">
-        <v>0.05207797</v>
+        <v>0.05514138</v>
       </c>
       <c r="N19">
-        <v>0.43592203</v>
+        <v>0.43285862</v>
       </c>
       <c r="O19">
-        <v>0.08718440599999999</v>
+        <v>0.086571724</v>
       </c>
       <c r="P19">
-        <v>0.348737624</v>
+        <v>0.346286896</v>
       </c>
       <c r="Q19">
-        <v>0.4347376239999999</v>
+        <v>0.4322868959999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1224737780954277</v>
+        <v>0.1232481433743797</v>
       </c>
       <c r="T19">
-        <v>1.186118961952759</v>
+        <v>1.198098146540476</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -3002,7 +3002,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>9.3705649432956</v>
+        <v>8.8499780020014</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3010,22 +3010,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1087674775669913</v>
+        <v>0.1086057193147777</v>
       </c>
       <c r="C20">
-        <v>4.795448785727136</v>
+        <v>4.744025276984137</v>
       </c>
       <c r="D20">
-        <v>2.266128785727136</v>
+        <v>2.271965276984136</v>
       </c>
       <c r="E20">
-        <v>0.96468</v>
+        <v>1.02194</v>
       </c>
       <c r="F20">
-        <v>1.03068</v>
+        <v>1.08794</v>
       </c>
       <c r="G20">
         <v>3.56</v>
@@ -3046,28 +3046,28 @@
         <v>0.488</v>
       </c>
       <c r="M20">
-        <v>0.05514138</v>
+        <v>0.05820478999999999</v>
       </c>
       <c r="N20">
-        <v>0.43285862</v>
+        <v>0.42979521</v>
       </c>
       <c r="O20">
-        <v>0.086571724</v>
+        <v>0.085959042</v>
       </c>
       <c r="P20">
-        <v>0.346286896</v>
+        <v>0.343836168</v>
       </c>
       <c r="Q20">
-        <v>0.4322868959999999</v>
+        <v>0.429836168</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1232481433743796</v>
+        <v>0.1240416287836761</v>
       </c>
       <c r="T20">
-        <v>1.198098146540475</v>
+        <v>1.210373113463691</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -3084,7 +3084,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.8499780020014</v>
+        <v>8.384189686106591</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3092,22 +3092,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1086057193147777</v>
+        <v>0.108443961062564</v>
       </c>
       <c r="C21">
-        <v>4.744025276984137</v>
+        <v>4.69263191003322</v>
       </c>
       <c r="D21">
-        <v>2.271965276984136</v>
+        <v>2.277831910033219</v>
       </c>
       <c r="E21">
-        <v>1.02194</v>
+        <v>1.0792</v>
       </c>
       <c r="F21">
-        <v>1.08794</v>
+        <v>1.1452</v>
       </c>
       <c r="G21">
         <v>3.56</v>
@@ -3128,28 +3128,28 @@
         <v>0.488</v>
       </c>
       <c r="M21">
-        <v>0.05820478999999999</v>
+        <v>0.0612682</v>
       </c>
       <c r="N21">
-        <v>0.42979521</v>
+        <v>0.4267318</v>
       </c>
       <c r="O21">
-        <v>0.085959042</v>
+        <v>0.08534636000000001</v>
       </c>
       <c r="P21">
-        <v>0.343836168</v>
+        <v>0.34138544</v>
       </c>
       <c r="Q21">
-        <v>0.429836168</v>
+        <v>0.4273854399999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1240416287836761</v>
+        <v>0.124854951328205</v>
       </c>
       <c r="T21">
-        <v>1.210373113463691</v>
+        <v>1.222954954559987</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.384189686106591</v>
+        <v>7.964980201801261</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3174,22 +3174,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.108443961062564</v>
+        <v>0.1084166028103503</v>
       </c>
       <c r="C22">
-        <v>4.69263191003322</v>
+        <v>4.636367133298265</v>
       </c>
       <c r="D22">
-        <v>2.277831910033219</v>
+        <v>2.278827133298265</v>
       </c>
       <c r="E22">
-        <v>1.0792</v>
+        <v>1.13646</v>
       </c>
       <c r="F22">
-        <v>1.1452</v>
+        <v>1.20246</v>
       </c>
       <c r="G22">
         <v>3.56</v>
@@ -3210,45 +3210,45 @@
         <v>0.488</v>
       </c>
       <c r="M22">
-        <v>0.0612682</v>
+        <v>0.065293578</v>
       </c>
       <c r="N22">
-        <v>0.4267318</v>
+        <v>0.422706422</v>
       </c>
       <c r="O22">
-        <v>0.08534636000000001</v>
+        <v>0.0845412844</v>
       </c>
       <c r="P22">
-        <v>0.34138544</v>
+        <v>0.3381651376</v>
       </c>
       <c r="Q22">
-        <v>0.4273854399999999</v>
+        <v>0.4241651376</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.124854951328205</v>
+        <v>0.1256888643168991</v>
       </c>
       <c r="T22">
-        <v>1.222954954559987</v>
+        <v>1.235855323278975</v>
       </c>
       <c r="U22">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V22">
         <v>0.2</v>
       </c>
       <c r="W22">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y22">
-        <v>7.964980201801261</v>
+        <v>7.473935644941987</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3256,22 +3256,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1084166028103503</v>
+        <v>0.1082612445581366</v>
       </c>
       <c r="C23">
-        <v>4.636367133298265</v>
+        <v>4.584775201602554</v>
       </c>
       <c r="D23">
-        <v>2.278827133298265</v>
+        <v>2.284495201602553</v>
       </c>
       <c r="E23">
-        <v>1.13646</v>
+        <v>1.19372</v>
       </c>
       <c r="F23">
-        <v>1.20246</v>
+        <v>1.25972</v>
       </c>
       <c r="G23">
         <v>3.56</v>
@@ -3292,28 +3292,28 @@
         <v>0.488</v>
       </c>
       <c r="M23">
-        <v>0.06529357799999999</v>
+        <v>0.068402796</v>
       </c>
       <c r="N23">
-        <v>0.422706422</v>
+        <v>0.419597204</v>
       </c>
       <c r="O23">
-        <v>0.0845412844</v>
+        <v>0.08391944080000001</v>
       </c>
       <c r="P23">
-        <v>0.3381651376</v>
+        <v>0.3356777632</v>
       </c>
       <c r="Q23">
-        <v>0.4241651376</v>
+        <v>0.4216777631999999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1256888643168991</v>
+        <v>0.1265441596899188</v>
       </c>
       <c r="T23">
-        <v>1.235855323278975</v>
+        <v>1.249086470683064</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3330,7 +3330,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.473935644941989</v>
+        <v>7.134211297444625</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3338,22 +3338,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1082612445581366</v>
+        <v>0.108105886305923</v>
       </c>
       <c r="C24">
-        <v>4.584775201602554</v>
+        <v>4.533211536295055</v>
       </c>
       <c r="D24">
-        <v>2.284495201602553</v>
+        <v>2.290191536295055</v>
       </c>
       <c r="E24">
-        <v>1.19372</v>
+        <v>1.25098</v>
       </c>
       <c r="F24">
-        <v>1.25972</v>
+        <v>1.31698</v>
       </c>
       <c r="G24">
         <v>3.56</v>
@@ -3374,28 +3374,28 @@
         <v>0.488</v>
       </c>
       <c r="M24">
-        <v>0.068402796</v>
+        <v>0.071512014</v>
       </c>
       <c r="N24">
-        <v>0.419597204</v>
+        <v>0.416487986</v>
       </c>
       <c r="O24">
-        <v>0.08391944080000001</v>
+        <v>0.0832975972</v>
       </c>
       <c r="P24">
-        <v>0.3356777632</v>
+        <v>0.3331903888</v>
       </c>
       <c r="Q24">
-        <v>0.4216777631999999</v>
+        <v>0.4191903887999999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1265441596899188</v>
+        <v>0.1274216705271727</v>
       </c>
       <c r="T24">
-        <v>1.249086470683064</v>
+        <v>1.262661284253494</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3412,7 +3412,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.134211297444625</v>
+        <v>6.824028197555728</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3420,22 +3420,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.108105886305923</v>
+        <v>0.1079505280537093</v>
       </c>
       <c r="C25">
-        <v>4.533211536295055</v>
+        <v>4.48167634934903</v>
       </c>
       <c r="D25">
-        <v>2.290191536295055</v>
+        <v>2.295916349349031</v>
       </c>
       <c r="E25">
-        <v>1.25098</v>
+        <v>1.30824</v>
       </c>
       <c r="F25">
-        <v>1.31698</v>
+        <v>1.37424</v>
       </c>
       <c r="G25">
         <v>3.56</v>
@@ -3456,28 +3456,28 @@
         <v>0.488</v>
       </c>
       <c r="M25">
-        <v>0.071512014</v>
+        <v>0.07462123200000001</v>
       </c>
       <c r="N25">
-        <v>0.416487986</v>
+        <v>0.413378768</v>
       </c>
       <c r="O25">
-        <v>0.0832975972</v>
+        <v>0.0826757536</v>
       </c>
       <c r="P25">
-        <v>0.3331903888</v>
+        <v>0.3307030143999999</v>
       </c>
       <c r="Q25">
-        <v>0.4191903887999999</v>
+        <v>0.4167030143999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1274216705271727</v>
+        <v>0.1283222737548806</v>
       </c>
       <c r="T25">
-        <v>1.262661284253494</v>
+        <v>1.276593329759987</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.824028197555728</v>
+        <v>6.539693689324238</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3502,22 +3502,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1079505280537092</v>
+        <v>0.1077951698014956</v>
       </c>
       <c r="C26">
-        <v>4.481676349349032</v>
+        <v>4.430169854862537</v>
       </c>
       <c r="D26">
-        <v>2.295916349349032</v>
+        <v>2.301669854862537</v>
       </c>
       <c r="E26">
-        <v>1.30824</v>
+        <v>1.3655</v>
       </c>
       <c r="F26">
-        <v>1.37424</v>
+        <v>1.4315</v>
       </c>
       <c r="G26">
         <v>3.56</v>
@@ -3538,28 +3538,28 @@
         <v>0.488</v>
       </c>
       <c r="M26">
-        <v>0.074621232</v>
+        <v>0.07773045000000001</v>
       </c>
       <c r="N26">
-        <v>0.413378768</v>
+        <v>0.41026955</v>
       </c>
       <c r="O26">
-        <v>0.08267575360000001</v>
+        <v>0.08205391000000001</v>
       </c>
       <c r="P26">
-        <v>0.3307030144</v>
+        <v>0.32821564</v>
       </c>
       <c r="Q26">
-        <v>0.4167030144</v>
+        <v>0.4142156399999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1283222737548806</v>
+        <v>0.1292468930686608</v>
       </c>
       <c r="T26">
-        <v>1.276593329759987</v>
+        <v>1.290896896479987</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3576,7 +3576,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.53969368932424</v>
+        <v>6.278105941751269</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3584,22 +3584,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1077951698014956</v>
+        <v>0.1078478115492819</v>
       </c>
       <c r="C27">
-        <v>4.430169854862537</v>
+        <v>4.370957103895796</v>
       </c>
       <c r="D27">
-        <v>2.301669854862537</v>
+        <v>2.299717103895796</v>
       </c>
       <c r="E27">
-        <v>1.3655</v>
+        <v>1.42276</v>
       </c>
       <c r="F27">
-        <v>1.4315</v>
+        <v>1.48876</v>
       </c>
       <c r="G27">
         <v>3.56</v>
@@ -3620,45 +3620,45 @@
         <v>0.488</v>
       </c>
       <c r="M27">
-        <v>0.07773045000000001</v>
+        <v>0.08232842800000001</v>
       </c>
       <c r="N27">
-        <v>0.41026955</v>
+        <v>0.405671572</v>
       </c>
       <c r="O27">
-        <v>0.08205391000000001</v>
+        <v>0.0811343144</v>
       </c>
       <c r="P27">
-        <v>0.32821564</v>
+        <v>0.3245372576</v>
       </c>
       <c r="Q27">
-        <v>0.4142156399999999</v>
+        <v>0.4105372575999999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1292468930686608</v>
+        <v>0.1301965020936242</v>
       </c>
       <c r="T27">
-        <v>1.290896896479987</v>
+        <v>1.305587046084311</v>
       </c>
       <c r="U27">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V27">
         <v>0.2</v>
       </c>
       <c r="W27">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y27">
-        <v>6.278105941751269</v>
+        <v>5.927478659011927</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3666,22 +3666,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1078478115492819</v>
+        <v>0.1077004532970682</v>
       </c>
       <c r="C28">
-        <v>4.370957103895796</v>
+        <v>4.319171737359135</v>
       </c>
       <c r="D28">
-        <v>2.299717103895796</v>
+        <v>2.305191737359134</v>
       </c>
       <c r="E28">
-        <v>1.42276</v>
+        <v>1.48002</v>
       </c>
       <c r="F28">
-        <v>1.48876</v>
+        <v>1.54602</v>
       </c>
       <c r="G28">
         <v>3.56</v>
@@ -3702,28 +3702,28 @@
         <v>0.488</v>
       </c>
       <c r="M28">
-        <v>0.08232842800000001</v>
+        <v>0.08549490600000001</v>
       </c>
       <c r="N28">
-        <v>0.405671572</v>
+        <v>0.402505094</v>
       </c>
       <c r="O28">
-        <v>0.0811343144</v>
+        <v>0.0805010188</v>
       </c>
       <c r="P28">
-        <v>0.3245372576</v>
+        <v>0.3220040752</v>
       </c>
       <c r="Q28">
-        <v>0.4105372575999999</v>
+        <v>0.4080040752</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1301965020936242</v>
+        <v>0.1311721278042031</v>
       </c>
       <c r="T28">
-        <v>1.305587046084311</v>
+        <v>1.320679665540808</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3740,7 +3740,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.927478659011927</v>
+        <v>5.707942412381855</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3748,22 +3748,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1077004532970682</v>
+        <v>0.1075530950448546</v>
       </c>
       <c r="C29">
-        <v>4.319171737359135</v>
+        <v>4.267412498498118</v>
       </c>
       <c r="D29">
-        <v>2.305191737359134</v>
+        <v>2.310692498498118</v>
       </c>
       <c r="E29">
-        <v>1.48002</v>
+        <v>1.53728</v>
       </c>
       <c r="F29">
-        <v>1.54602</v>
+        <v>1.60328</v>
       </c>
       <c r="G29">
         <v>3.56</v>
@@ -3784,28 +3784,28 @@
         <v>0.488</v>
       </c>
       <c r="M29">
-        <v>0.08549490600000001</v>
+        <v>0.08866138400000001</v>
       </c>
       <c r="N29">
-        <v>0.402505094</v>
+        <v>0.399338616</v>
       </c>
       <c r="O29">
-        <v>0.0805010188</v>
+        <v>0.0798677232</v>
       </c>
       <c r="P29">
-        <v>0.3220040752</v>
+        <v>0.3194708928</v>
       </c>
       <c r="Q29">
-        <v>0.4080040752</v>
+        <v>0.4054708927999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1311721278042031</v>
+        <v>0.1321748542289647</v>
       </c>
       <c r="T29">
-        <v>1.320679665540808</v>
+        <v>1.336191524426653</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3822,7 +3822,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.707942412381855</v>
+        <v>5.504087326225361</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3830,22 +3830,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1075530950448546</v>
+        <v>0.1074057367926409</v>
       </c>
       <c r="C30">
-        <v>4.267412498498118</v>
+        <v>4.215679574801547</v>
       </c>
       <c r="D30">
-        <v>2.310692498498118</v>
+        <v>2.316219574801548</v>
       </c>
       <c r="E30">
-        <v>1.53728</v>
+        <v>1.59454</v>
       </c>
       <c r="F30">
-        <v>1.60328</v>
+        <v>1.66054</v>
       </c>
       <c r="G30">
         <v>3.56</v>
@@ -3866,28 +3866,28 @@
         <v>0.488</v>
       </c>
       <c r="M30">
-        <v>0.08866138400000001</v>
+        <v>0.09182786200000001</v>
       </c>
       <c r="N30">
-        <v>0.399338616</v>
+        <v>0.396172138</v>
       </c>
       <c r="O30">
-        <v>0.0798677232</v>
+        <v>0.07923442759999999</v>
       </c>
       <c r="P30">
-        <v>0.3194708928</v>
+        <v>0.3169377104</v>
       </c>
       <c r="Q30">
-        <v>0.4054708927999999</v>
+        <v>0.4029377103999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1321748542289647</v>
+        <v>0.1332058264685083</v>
       </c>
       <c r="T30">
-        <v>1.336191524426653</v>
+        <v>1.35214033708393</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3904,7 +3904,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.504087326225361</v>
+        <v>5.314291211527934</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3912,22 +3912,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1074057367926409</v>
+        <v>0.1072583785404272</v>
       </c>
       <c r="C31">
-        <v>4.215679574801547</v>
+        <v>4.163973155556388</v>
       </c>
       <c r="D31">
-        <v>2.316219574801548</v>
+        <v>2.321773155556388</v>
       </c>
       <c r="E31">
-        <v>1.59454</v>
+        <v>1.6518</v>
       </c>
       <c r="F31">
-        <v>1.66054</v>
+        <v>1.7178</v>
       </c>
       <c r="G31">
         <v>3.56</v>
@@ -3948,28 +3948,28 @@
         <v>0.488</v>
       </c>
       <c r="M31">
-        <v>0.091827862</v>
+        <v>0.09499434</v>
       </c>
       <c r="N31">
-        <v>0.396172138</v>
+        <v>0.39300566</v>
       </c>
       <c r="O31">
-        <v>0.0792344276</v>
+        <v>0.078601132</v>
       </c>
       <c r="P31">
-        <v>0.3169377104</v>
+        <v>0.314404528</v>
       </c>
       <c r="Q31">
-        <v>0.4029377104</v>
+        <v>0.4004045279999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1332058264685083</v>
+        <v>0.1342662550577532</v>
       </c>
       <c r="T31">
-        <v>1.35214033708393</v>
+        <v>1.368544830102843</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3986,7 +3986,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.314291211527935</v>
+        <v>5.13714817114367</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3994,22 +3994,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1072583785404272</v>
+        <v>0.1071110202882135</v>
       </c>
       <c r="C32">
-        <v>4.163973155556388</v>
+        <v>4.112293431869376</v>
       </c>
       <c r="D32">
-        <v>2.321773155556388</v>
+        <v>2.327353431869376</v>
       </c>
       <c r="E32">
-        <v>1.6518</v>
+        <v>1.70906</v>
       </c>
       <c r="F32">
-        <v>1.7178</v>
+        <v>1.77506</v>
       </c>
       <c r="G32">
         <v>3.56</v>
@@ -4030,28 +4030,28 @@
         <v>0.488</v>
       </c>
       <c r="M32">
-        <v>0.09499434</v>
+        <v>0.09816081800000001</v>
       </c>
       <c r="N32">
-        <v>0.39300566</v>
+        <v>0.389839182</v>
       </c>
       <c r="O32">
-        <v>0.078601132</v>
+        <v>0.0779678364</v>
       </c>
       <c r="P32">
-        <v>0.314404528</v>
+        <v>0.3118713456</v>
       </c>
       <c r="Q32">
-        <v>0.4004045279999999</v>
+        <v>0.3978713456</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1342662550577532</v>
+        <v>0.1353574207075559</v>
       </c>
       <c r="T32">
-        <v>1.368544830102843</v>
+        <v>1.385424815673029</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -4068,7 +4068,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.13714817114367</v>
+        <v>4.971433714010002</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4076,22 +4076,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1071110202882135</v>
+        <v>0.1069636620359999</v>
       </c>
       <c r="C33">
-        <v>4.112293431869376</v>
+        <v>4.060640596688937</v>
       </c>
       <c r="D33">
-        <v>2.327353431869376</v>
+        <v>2.332960596688937</v>
       </c>
       <c r="E33">
-        <v>1.70906</v>
+        <v>1.76632</v>
       </c>
       <c r="F33">
-        <v>1.77506</v>
+        <v>1.83232</v>
       </c>
       <c r="G33">
         <v>3.56</v>
@@ -4112,28 +4112,28 @@
         <v>0.488</v>
       </c>
       <c r="M33">
-        <v>0.09816081800000001</v>
+        <v>0.101327296</v>
       </c>
       <c r="N33">
-        <v>0.389839182</v>
+        <v>0.386672704</v>
       </c>
       <c r="O33">
-        <v>0.0779678364</v>
+        <v>0.0773345408</v>
       </c>
       <c r="P33">
-        <v>0.3118713456</v>
+        <v>0.3093381632</v>
       </c>
       <c r="Q33">
-        <v>0.3978713456</v>
+        <v>0.3953381631999999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1353574207075559</v>
+        <v>0.1364806794647057</v>
       </c>
       <c r="T33">
-        <v>1.385424815673029</v>
+        <v>1.402801271407044</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4150,7 +4150,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.971433714010002</v>
+        <v>4.816076410447191</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4158,22 +4158,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1069636620359999</v>
+        <v>0.1068163037837862</v>
       </c>
       <c r="C34">
-        <v>4.060640596688937</v>
+        <v>4.009014844827428</v>
       </c>
       <c r="D34">
-        <v>2.332960596688937</v>
+        <v>2.338594844827429</v>
       </c>
       <c r="E34">
-        <v>1.76632</v>
+        <v>1.82358</v>
       </c>
       <c r="F34">
-        <v>1.83232</v>
+        <v>1.88958</v>
       </c>
       <c r="G34">
         <v>3.56</v>
@@ -4194,28 +4194,28 @@
         <v>0.488</v>
       </c>
       <c r="M34">
-        <v>0.101327296</v>
+        <v>0.104493774</v>
       </c>
       <c r="N34">
-        <v>0.386672704</v>
+        <v>0.383506226</v>
       </c>
       <c r="O34">
-        <v>0.0773345408</v>
+        <v>0.07670124519999999</v>
       </c>
       <c r="P34">
-        <v>0.3093381632</v>
+        <v>0.3068049808</v>
       </c>
       <c r="Q34">
-        <v>0.3953381631999999</v>
+        <v>0.3928049807999999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1364806794647057</v>
+        <v>0.1376374683340092</v>
       </c>
       <c r="T34">
-        <v>1.402801271407044</v>
+        <v>1.420696427312224</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4232,7 +4232,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.816076410447191</v>
+        <v>4.670134701039699</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4240,22 +4240,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1068163037837862</v>
+        <v>0.1066689455315725</v>
       </c>
       <c r="C35">
-        <v>4.009014844827428</v>
+        <v>3.957416372983703</v>
       </c>
       <c r="D35">
-        <v>2.338594844827429</v>
+        <v>2.344256372983703</v>
       </c>
       <c r="E35">
-        <v>1.82358</v>
+        <v>1.88084</v>
       </c>
       <c r="F35">
-        <v>1.88958</v>
+        <v>1.94684</v>
       </c>
       <c r="G35">
         <v>3.56</v>
@@ -4276,28 +4276,28 @@
         <v>0.488</v>
       </c>
       <c r="M35">
-        <v>0.104493774</v>
+        <v>0.107660252</v>
       </c>
       <c r="N35">
-        <v>0.383506226</v>
+        <v>0.380339748</v>
       </c>
       <c r="O35">
-        <v>0.07670124519999999</v>
+        <v>0.0760679496</v>
       </c>
       <c r="P35">
-        <v>0.3068049808</v>
+        <v>0.3042717984</v>
       </c>
       <c r="Q35">
-        <v>0.3928049807999999</v>
+        <v>0.3902717983999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1376374683340092</v>
+        <v>0.1388293114114735</v>
       </c>
       <c r="T35">
-        <v>1.420696427312224</v>
+        <v>1.439133860669076</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4314,7 +4314,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.670134701039699</v>
+        <v>4.532777798067944</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4322,22 +4322,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1066689455315725</v>
+        <v>0.1072215872793588</v>
       </c>
       <c r="C36">
-        <v>3.957416372983703</v>
+        <v>3.879063887481291</v>
       </c>
       <c r="D36">
-        <v>2.344256372983703</v>
+        <v>2.323163887481292</v>
       </c>
       <c r="E36">
-        <v>1.88084</v>
+        <v>1.9381</v>
       </c>
       <c r="F36">
-        <v>1.94684</v>
+        <v>2.0041</v>
       </c>
       <c r="G36">
         <v>3.56</v>
@@ -4358,45 +4358,45 @@
         <v>0.488</v>
       </c>
       <c r="M36">
-        <v>0.107660252</v>
+        <v>0.11583698</v>
       </c>
       <c r="N36">
-        <v>0.380339748</v>
+        <v>0.37216302</v>
       </c>
       <c r="O36">
-        <v>0.0760679496</v>
+        <v>0.074432604</v>
       </c>
       <c r="P36">
-        <v>0.3042717984</v>
+        <v>0.2977304159999999</v>
       </c>
       <c r="Q36">
-        <v>0.3902717983999999</v>
+        <v>0.3837304159999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1388293114114735</v>
+        <v>0.140057826583629</v>
       </c>
       <c r="T36">
-        <v>1.439133860669076</v>
+        <v>1.458138599667677</v>
       </c>
       <c r="U36">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V36">
         <v>0.2</v>
       </c>
       <c r="W36">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y36">
-        <v>4.532777798067944</v>
+        <v>4.21281701232197</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4404,22 +4404,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1072215872793588</v>
+        <v>0.1070942290271452</v>
       </c>
       <c r="C37">
-        <v>3.879063887481291</v>
+        <v>3.826630999217774</v>
       </c>
       <c r="D37">
-        <v>2.323163887481292</v>
+        <v>2.327990999217773</v>
       </c>
       <c r="E37">
-        <v>1.9381</v>
+        <v>1.99536</v>
       </c>
       <c r="F37">
-        <v>2.0041</v>
+        <v>2.06136</v>
       </c>
       <c r="G37">
         <v>3.56</v>
@@ -4440,28 +4440,28 @@
         <v>0.488</v>
       </c>
       <c r="M37">
-        <v>0.11583698</v>
+        <v>0.119146608</v>
       </c>
       <c r="N37">
-        <v>0.37216302</v>
+        <v>0.368853392</v>
       </c>
       <c r="O37">
-        <v>0.074432604</v>
+        <v>0.0737706784</v>
       </c>
       <c r="P37">
-        <v>0.2977304159999999</v>
+        <v>0.2950827136</v>
       </c>
       <c r="Q37">
-        <v>0.3837304159999999</v>
+        <v>0.3810827136</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.140057826583629</v>
+        <v>0.1413247328549143</v>
       </c>
       <c r="T37">
-        <v>1.458138599667677</v>
+        <v>1.477737236759985</v>
       </c>
       <c r="U37">
         <v>0.0578</v>
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.21281701232197</v>
+        <v>4.095794317535249</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4486,22 +4486,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1070942290271452</v>
+        <v>0.1080028707749315</v>
       </c>
       <c r="C38">
-        <v>3.826630999217774</v>
+        <v>3.735364372449471</v>
       </c>
       <c r="D38">
-        <v>2.327990999217773</v>
+        <v>2.29398437244947</v>
       </c>
       <c r="E38">
-        <v>1.99536</v>
+        <v>2.05262</v>
       </c>
       <c r="F38">
-        <v>2.06136</v>
+        <v>2.11862</v>
       </c>
       <c r="G38">
         <v>3.56</v>
@@ -4522,45 +4522,45 @@
         <v>0.488</v>
       </c>
       <c r="M38">
-        <v>0.119146608</v>
+        <v>0.129871406</v>
       </c>
       <c r="N38">
-        <v>0.368853392</v>
+        <v>0.358128594</v>
       </c>
       <c r="O38">
-        <v>0.0737706784</v>
+        <v>0.0716257188</v>
       </c>
       <c r="P38">
-        <v>0.2950827136</v>
+        <v>0.2865028752</v>
       </c>
       <c r="Q38">
-        <v>0.3810827136</v>
+        <v>0.3725028751999999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1413247328549143</v>
+        <v>0.1426318583729071</v>
       </c>
       <c r="T38">
-        <v>1.477737236759985</v>
+        <v>1.497958052807604</v>
       </c>
       <c r="U38">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V38">
         <v>0.2</v>
       </c>
       <c r="W38">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y38">
-        <v>4.095794317535249</v>
+        <v>3.757563077433689</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4568,22 +4568,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1080028707749315</v>
+        <v>0.1079035125227178</v>
       </c>
       <c r="C39">
-        <v>3.735364372449471</v>
+        <v>3.681774475292184</v>
       </c>
       <c r="D39">
-        <v>2.29398437244947</v>
+        <v>2.297654475292183</v>
       </c>
       <c r="E39">
-        <v>2.05262</v>
+        <v>2.10988</v>
       </c>
       <c r="F39">
-        <v>2.11862</v>
+        <v>2.17588</v>
       </c>
       <c r="G39">
         <v>3.56</v>
@@ -4604,28 +4604,28 @@
         <v>0.488</v>
       </c>
       <c r="M39">
-        <v>0.129871406</v>
+        <v>0.133381444</v>
       </c>
       <c r="N39">
-        <v>0.358128594</v>
+        <v>0.354618556</v>
       </c>
       <c r="O39">
-        <v>0.0716257188</v>
+        <v>0.0709237112</v>
       </c>
       <c r="P39">
-        <v>0.2865028752</v>
+        <v>0.2836948448</v>
       </c>
       <c r="Q39">
-        <v>0.3725028751999999</v>
+        <v>0.3696948448</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1426318583729071</v>
+        <v>0.14398114923019</v>
       </c>
       <c r="T39">
-        <v>1.497958052807604</v>
+        <v>1.518831153243855</v>
       </c>
       <c r="U39">
         <v>0.0613</v>
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.757563077433689</v>
+        <v>3.658679838553855</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4650,22 +4650,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1079035125227178</v>
+        <v>0.1078041542705041</v>
       </c>
       <c r="C40">
-        <v>3.681774475292184</v>
+        <v>3.628196340411414</v>
       </c>
       <c r="D40">
-        <v>2.297654475292183</v>
+        <v>2.301336340411414</v>
       </c>
       <c r="E40">
-        <v>2.10988</v>
+        <v>2.16714</v>
       </c>
       <c r="F40">
-        <v>2.17588</v>
+        <v>2.23314</v>
       </c>
       <c r="G40">
         <v>3.56</v>
@@ -4686,28 +4686,28 @@
         <v>0.488</v>
       </c>
       <c r="M40">
-        <v>0.133381444</v>
+        <v>0.136891482</v>
       </c>
       <c r="N40">
-        <v>0.354618556</v>
+        <v>0.351108518</v>
       </c>
       <c r="O40">
-        <v>0.0709237112</v>
+        <v>0.0702217036</v>
       </c>
       <c r="P40">
-        <v>0.2836948448</v>
+        <v>0.2808868144</v>
       </c>
       <c r="Q40">
-        <v>0.3696948448</v>
+        <v>0.3668868143999999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.14398114923019</v>
+        <v>0.145374679131974</v>
       </c>
       <c r="T40">
-        <v>1.518831153243855</v>
+        <v>1.540388617628837</v>
       </c>
       <c r="U40">
         <v>0.0613</v>
@@ -4724,7 +4724,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.658679838553855</v>
+        <v>3.564867535001191</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4732,22 +4732,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1078041542705041</v>
+        <v>0.1086007960182905</v>
       </c>
       <c r="C41">
-        <v>3.628196340411414</v>
+        <v>3.541743388718006</v>
       </c>
       <c r="D41">
-        <v>2.301336340411414</v>
+        <v>2.272143388718005</v>
       </c>
       <c r="E41">
-        <v>2.16714</v>
+        <v>2.2244</v>
       </c>
       <c r="F41">
-        <v>2.23314</v>
+        <v>2.2904</v>
       </c>
       <c r="G41">
         <v>3.56</v>
@@ -4768,45 +4768,45 @@
         <v>0.488</v>
       </c>
       <c r="M41">
-        <v>0.136891482</v>
+        <v>0.14681464</v>
       </c>
       <c r="N41">
-        <v>0.351108518</v>
+        <v>0.34118536</v>
       </c>
       <c r="O41">
-        <v>0.0702217036</v>
+        <v>0.068237072</v>
       </c>
       <c r="P41">
-        <v>0.2808868144</v>
+        <v>0.272948288</v>
       </c>
       <c r="Q41">
-        <v>0.3668868143999999</v>
+        <v>0.3589482879999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.145374679131974</v>
+        <v>0.1468146600304841</v>
       </c>
       <c r="T41">
-        <v>1.540388617628837</v>
+        <v>1.562664664159984</v>
       </c>
       <c r="U41">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V41">
         <v>0.2</v>
       </c>
       <c r="W41">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y41">
-        <v>3.564867535001191</v>
+        <v>3.323919194979465</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4814,22 +4814,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1086007960182905</v>
+        <v>0.1085238377660768</v>
       </c>
       <c r="C42">
-        <v>3.541743388718006</v>
+        <v>3.487271167498805</v>
       </c>
       <c r="D42">
-        <v>2.272143388718005</v>
+        <v>2.274931167498805</v>
       </c>
       <c r="E42">
-        <v>2.2244</v>
+        <v>2.28166</v>
       </c>
       <c r="F42">
-        <v>2.2904</v>
+        <v>2.34766</v>
       </c>
       <c r="G42">
         <v>3.56</v>
@@ -4850,28 +4850,28 @@
         <v>0.488</v>
       </c>
       <c r="M42">
-        <v>0.14681464</v>
+        <v>0.150485006</v>
       </c>
       <c r="N42">
-        <v>0.34118536</v>
+        <v>0.337514994</v>
       </c>
       <c r="O42">
-        <v>0.068237072</v>
+        <v>0.06750299879999999</v>
       </c>
       <c r="P42">
-        <v>0.272948288</v>
+        <v>0.2700119952</v>
       </c>
       <c r="Q42">
-        <v>0.3589482879999999</v>
+        <v>0.3560119951999999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1468146600304841</v>
+        <v>0.1483034538408081</v>
       </c>
       <c r="T42">
-        <v>1.562664664159984</v>
+        <v>1.585695830912526</v>
       </c>
       <c r="U42">
         <v>0.0641</v>
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.323919194979465</v>
+        <v>3.242847995101917</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4896,22 +4896,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1085238377660768</v>
+        <v>0.1084468795138631</v>
       </c>
       <c r="C43">
-        <v>3.487271167498805</v>
+        <v>3.432805795545975</v>
       </c>
       <c r="D43">
-        <v>2.274931167498805</v>
+        <v>2.277725795545976</v>
       </c>
       <c r="E43">
-        <v>2.28166</v>
+        <v>2.33892</v>
       </c>
       <c r="F43">
-        <v>2.34766</v>
+        <v>2.40492</v>
       </c>
       <c r="G43">
         <v>3.56</v>
@@ -4932,28 +4932,28 @@
         <v>0.488</v>
       </c>
       <c r="M43">
-        <v>0.150485006</v>
+        <v>0.154155372</v>
       </c>
       <c r="N43">
-        <v>0.337514994</v>
+        <v>0.333844628</v>
       </c>
       <c r="O43">
-        <v>0.06750299879999999</v>
+        <v>0.0667689256</v>
       </c>
       <c r="P43">
-        <v>0.2700119952</v>
+        <v>0.2670757024</v>
       </c>
       <c r="Q43">
-        <v>0.3560119951999999</v>
+        <v>0.3530757024</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1483034538408081</v>
+        <v>0.1498435853687295</v>
       </c>
       <c r="T43">
-        <v>1.585695830912526</v>
+        <v>1.609521175828949</v>
       </c>
       <c r="U43">
         <v>0.0641</v>
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.242847995101917</v>
+        <v>3.165637328551871</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4978,22 +4978,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1084468795138631</v>
+        <v>0.1083699212616494</v>
       </c>
       <c r="C44">
-        <v>3.432805795545976</v>
+        <v>3.378347298132405</v>
       </c>
       <c r="D44">
-        <v>2.277725795545976</v>
+        <v>2.280527298132405</v>
       </c>
       <c r="E44">
-        <v>2.33892</v>
+        <v>2.39618</v>
       </c>
       <c r="F44">
-        <v>2.40492</v>
+        <v>2.46218</v>
       </c>
       <c r="G44">
         <v>3.56</v>
@@ -5014,28 +5014,28 @@
         <v>0.488</v>
       </c>
       <c r="M44">
-        <v>0.154155372</v>
+        <v>0.157825738</v>
       </c>
       <c r="N44">
-        <v>0.333844628</v>
+        <v>0.330174262</v>
       </c>
       <c r="O44">
-        <v>0.06676892560000001</v>
+        <v>0.0660348524</v>
       </c>
       <c r="P44">
-        <v>0.2670757024</v>
+        <v>0.2641394096</v>
       </c>
       <c r="Q44">
-        <v>0.3530757024</v>
+        <v>0.3501394096</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1498435853687295</v>
+        <v>0.151437756599385</v>
       </c>
       <c r="T44">
-        <v>1.609521175828949</v>
+        <v>1.634182497759983</v>
       </c>
       <c r="U44">
         <v>0.0641</v>
@@ -5052,7 +5052,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.165637328551872</v>
+        <v>3.092017855794851</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5060,22 +5060,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1083699212616494</v>
+        <v>0.1082929630094358</v>
       </c>
       <c r="C45">
-        <v>3.378347298132405</v>
+        <v>3.323895700655475</v>
       </c>
       <c r="D45">
-        <v>2.280527298132405</v>
+        <v>2.283335700655475</v>
       </c>
       <c r="E45">
-        <v>2.39618</v>
+        <v>2.45344</v>
       </c>
       <c r="F45">
-        <v>2.46218</v>
+        <v>2.51944</v>
       </c>
       <c r="G45">
         <v>3.56</v>
@@ -5096,28 +5096,28 @@
         <v>0.488</v>
       </c>
       <c r="M45">
-        <v>0.157825738</v>
+        <v>0.161496104</v>
       </c>
       <c r="N45">
-        <v>0.330174262</v>
+        <v>0.326503896</v>
       </c>
       <c r="O45">
-        <v>0.0660348524</v>
+        <v>0.06530077919999999</v>
       </c>
       <c r="P45">
-        <v>0.2641394096</v>
+        <v>0.2612031168</v>
       </c>
       <c r="Q45">
-        <v>0.3501394096</v>
+        <v>0.3472031167999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.151437756599385</v>
+        <v>0.1530888625168496</v>
       </c>
       <c r="T45">
-        <v>1.634182497759983</v>
+        <v>1.659724581188554</v>
       </c>
       <c r="U45">
         <v>0.0641</v>
@@ -5134,7 +5134,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.092017855794851</v>
+        <v>3.021744722708605</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5142,22 +5142,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1082929630094358</v>
+        <v>0.1110240047572221</v>
       </c>
       <c r="C46">
-        <v>3.323895700655475</v>
+        <v>3.171028490611989</v>
       </c>
       <c r="D46">
-        <v>2.283335700655475</v>
+        <v>2.18772849061199</v>
       </c>
       <c r="E46">
-        <v>2.45344</v>
+        <v>2.5107</v>
       </c>
       <c r="F46">
-        <v>2.51944</v>
+        <v>2.5767</v>
       </c>
       <c r="G46">
         <v>3.56</v>
@@ -5178,45 +5178,45 @@
         <v>0.488</v>
       </c>
       <c r="M46">
-        <v>0.161496104</v>
+        <v>0.18526473</v>
       </c>
       <c r="N46">
-        <v>0.326503896</v>
+        <v>0.30273527</v>
       </c>
       <c r="O46">
-        <v>0.06530077919999999</v>
+        <v>0.060547054</v>
       </c>
       <c r="P46">
-        <v>0.2612031168</v>
+        <v>0.242188216</v>
       </c>
       <c r="Q46">
-        <v>0.3472031167999999</v>
+        <v>0.328188216</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1530888625168496</v>
+        <v>0.1548000086494947</v>
       </c>
       <c r="T46">
-        <v>1.659724581188554</v>
+        <v>1.686195467650892</v>
       </c>
       <c r="U46">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V46">
         <v>0.2</v>
       </c>
       <c r="W46">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y46">
-        <v>3.021744722708605</v>
+        <v>2.634068556923922</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5224,22 +5224,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1110240047572221</v>
+        <v>0.1110094465050084</v>
       </c>
       <c r="C47">
-        <v>3.171028490611989</v>
+        <v>3.11425690915943</v>
       </c>
       <c r="D47">
-        <v>2.18772849061199</v>
+        <v>2.18821690915943</v>
       </c>
       <c r="E47">
-        <v>2.5107</v>
+        <v>2.56796</v>
       </c>
       <c r="F47">
-        <v>2.5767</v>
+        <v>2.63396</v>
       </c>
       <c r="G47">
         <v>3.56</v>
@@ -5260,28 +5260,28 @@
         <v>0.488</v>
       </c>
       <c r="M47">
-        <v>0.18526473</v>
+        <v>0.189381724</v>
       </c>
       <c r="N47">
-        <v>0.30273527</v>
+        <v>0.298618276</v>
       </c>
       <c r="O47">
-        <v>0.060547054</v>
+        <v>0.0597236552</v>
       </c>
       <c r="P47">
-        <v>0.242188216</v>
+        <v>0.2388946208</v>
       </c>
       <c r="Q47">
-        <v>0.328188216</v>
+        <v>0.3248946207999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1548000086494947</v>
+        <v>0.1565745305648304</v>
       </c>
       <c r="T47">
-        <v>1.686195467650892</v>
+        <v>1.713646757315538</v>
       </c>
       <c r="U47">
         <v>0.07190000000000001</v>
@@ -5298,7 +5298,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.634068556923922</v>
+        <v>2.576806196990792</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5306,22 +5306,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1110094465050084</v>
+        <v>0.1109948882527947</v>
       </c>
       <c r="C48">
-        <v>3.11425690915943</v>
+        <v>3.057485545838095</v>
       </c>
       <c r="D48">
-        <v>2.18821690915943</v>
+        <v>2.188705545838095</v>
       </c>
       <c r="E48">
-        <v>2.56796</v>
+        <v>2.62522</v>
       </c>
       <c r="F48">
-        <v>2.63396</v>
+        <v>2.69122</v>
       </c>
       <c r="G48">
         <v>3.56</v>
@@ -5342,28 +5342,28 @@
         <v>0.488</v>
       </c>
       <c r="M48">
-        <v>0.189381724</v>
+        <v>0.193498718</v>
       </c>
       <c r="N48">
-        <v>0.298618276</v>
+        <v>0.294501282</v>
       </c>
       <c r="O48">
-        <v>0.0597236552</v>
+        <v>0.0589002564</v>
       </c>
       <c r="P48">
-        <v>0.2388946208</v>
+        <v>0.2356010256</v>
       </c>
       <c r="Q48">
-        <v>0.3248946207999999</v>
+        <v>0.3216010255999999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1565745305648304</v>
+        <v>0.1584160155713108</v>
       </c>
       <c r="T48">
-        <v>1.713646757315538</v>
+        <v>1.742133944703378</v>
       </c>
       <c r="U48">
         <v>0.07190000000000001</v>
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.576806196990792</v>
+        <v>2.521980533225031</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5388,22 +5388,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1109948882527947</v>
+        <v>0.1124779300005811</v>
       </c>
       <c r="C49">
-        <v>3.057485545838095</v>
+        <v>2.951544645005374</v>
       </c>
       <c r="D49">
-        <v>2.188705545838095</v>
+        <v>2.140024645005375</v>
       </c>
       <c r="E49">
-        <v>2.62522</v>
+        <v>2.68248</v>
       </c>
       <c r="F49">
-        <v>2.69122</v>
+        <v>2.74848</v>
       </c>
       <c r="G49">
         <v>3.56</v>
@@ -5424,45 +5424,45 @@
         <v>0.488</v>
       </c>
       <c r="M49">
-        <v>0.193498718</v>
+        <v>0.208334784</v>
       </c>
       <c r="N49">
-        <v>0.294501282</v>
+        <v>0.2796652159999999</v>
       </c>
       <c r="O49">
-        <v>0.0589002564</v>
+        <v>0.05593304319999999</v>
       </c>
       <c r="P49">
-        <v>0.2356010256</v>
+        <v>0.2237321728</v>
       </c>
       <c r="Q49">
-        <v>0.3216010255999999</v>
+        <v>0.3097321727999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1584160155713108</v>
+        <v>0.1603283269241944</v>
       </c>
       <c r="T49">
-        <v>1.742133944703378</v>
+        <v>1.771716793144597</v>
       </c>
       <c r="U49">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V49">
         <v>0.2</v>
       </c>
       <c r="W49">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y49">
-        <v>2.521980533225031</v>
+        <v>2.342383689513893</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5470,22 +5470,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1124779300005811</v>
+        <v>0.1124945717483674</v>
       </c>
       <c r="C50">
-        <v>2.951544645005375</v>
+        <v>2.893750662261874</v>
       </c>
       <c r="D50">
-        <v>2.140024645005375</v>
+        <v>2.139490662261875</v>
       </c>
       <c r="E50">
-        <v>2.68248</v>
+        <v>2.73974</v>
       </c>
       <c r="F50">
-        <v>2.74848</v>
+        <v>2.80574</v>
       </c>
       <c r="G50">
         <v>3.56</v>
@@ -5506,28 +5506,28 @@
         <v>0.488</v>
       </c>
       <c r="M50">
-        <v>0.208334784</v>
+        <v>0.212675092</v>
       </c>
       <c r="N50">
-        <v>0.279665216</v>
+        <v>0.275324908</v>
       </c>
       <c r="O50">
-        <v>0.0559330432</v>
+        <v>0.0550649816</v>
       </c>
       <c r="P50">
-        <v>0.2237321728</v>
+        <v>0.2202599264</v>
       </c>
       <c r="Q50">
-        <v>0.3097321728</v>
+        <v>0.3062599263999999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1603283269241944</v>
+        <v>0.1623156308791517</v>
       </c>
       <c r="T50">
-        <v>1.771716793144597</v>
+        <v>1.802459753289393</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.342383689513893</v>
+        <v>2.294579940748303</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5552,22 +5552,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1124945717483674</v>
+        <v>0.1125112134961537</v>
       </c>
       <c r="C51">
-        <v>2.893750662261874</v>
+        <v>2.835956945932542</v>
       </c>
       <c r="D51">
-        <v>2.139490662261875</v>
+        <v>2.138956945932542</v>
       </c>
       <c r="E51">
-        <v>2.73974</v>
+        <v>2.797</v>
       </c>
       <c r="F51">
-        <v>2.80574</v>
+        <v>2.863</v>
       </c>
       <c r="G51">
         <v>3.56</v>
@@ -5588,28 +5588,28 @@
         <v>0.488</v>
       </c>
       <c r="M51">
-        <v>0.212675092</v>
+        <v>0.2170154</v>
       </c>
       <c r="N51">
-        <v>0.275324908</v>
+        <v>0.2709846</v>
       </c>
       <c r="O51">
-        <v>0.0550649816</v>
+        <v>0.05419692</v>
       </c>
       <c r="P51">
-        <v>0.2202599264</v>
+        <v>0.21678768</v>
       </c>
       <c r="Q51">
-        <v>0.3062599263999999</v>
+        <v>0.3027876799999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1623156308791517</v>
+        <v>0.1643824269923074</v>
       </c>
       <c r="T51">
-        <v>1.802459753289393</v>
+        <v>1.834432431839981</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5626,7 +5626,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.294579940748303</v>
+        <v>2.248688341933337</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5634,22 +5634,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1125112134961537</v>
+        <v>0.11252785524394</v>
       </c>
       <c r="C52">
-        <v>2.835956945932542</v>
+        <v>2.778163495818045</v>
       </c>
       <c r="D52">
-        <v>2.138956945932542</v>
+        <v>2.138423495818045</v>
       </c>
       <c r="E52">
-        <v>2.797</v>
+        <v>2.85426</v>
       </c>
       <c r="F52">
-        <v>2.863</v>
+        <v>2.92026</v>
       </c>
       <c r="G52">
         <v>3.56</v>
@@ -5670,28 +5670,28 @@
         <v>0.488</v>
       </c>
       <c r="M52">
-        <v>0.2170154</v>
+        <v>0.221355708</v>
       </c>
       <c r="N52">
-        <v>0.2709846</v>
+        <v>0.2666442919999999</v>
       </c>
       <c r="O52">
-        <v>0.05419692</v>
+        <v>0.05332885839999999</v>
       </c>
       <c r="P52">
-        <v>0.21678768</v>
+        <v>0.2133154336</v>
       </c>
       <c r="Q52">
-        <v>0.3027876799999999</v>
+        <v>0.2993154335999999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1643824269923074</v>
+        <v>0.1665335821304899</v>
       </c>
       <c r="T52">
-        <v>1.834432431839981</v>
+        <v>1.867710117678348</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5708,7 +5708,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.248688341933337</v>
+        <v>2.204596413660134</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5716,22 +5716,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.11252785524394</v>
+        <v>0.1125444969917264</v>
       </c>
       <c r="C53">
-        <v>2.778163495818045</v>
+        <v>2.720370311719254</v>
       </c>
       <c r="D53">
-        <v>2.138423495818045</v>
+        <v>2.137890311719254</v>
       </c>
       <c r="E53">
-        <v>2.85426</v>
+        <v>2.91152</v>
       </c>
       <c r="F53">
-        <v>2.92026</v>
+        <v>2.97752</v>
       </c>
       <c r="G53">
         <v>3.56</v>
@@ -5752,28 +5752,28 @@
         <v>0.488</v>
       </c>
       <c r="M53">
-        <v>0.221355708</v>
+        <v>0.225696016</v>
       </c>
       <c r="N53">
-        <v>0.2666442919999999</v>
+        <v>0.262303984</v>
       </c>
       <c r="O53">
-        <v>0.05332885839999999</v>
+        <v>0.0524607968</v>
       </c>
       <c r="P53">
-        <v>0.2133154336</v>
+        <v>0.2098431872</v>
       </c>
       <c r="Q53">
-        <v>0.2993154335999999</v>
+        <v>0.2958431872</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1665335821304899</v>
+        <v>0.1687743687327633</v>
       </c>
       <c r="T53">
-        <v>1.867710117678348</v>
+        <v>1.902374373759981</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5790,7 +5790,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.204596413660134</v>
+        <v>2.162200328782055</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5798,22 +5798,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1125444969917264</v>
+        <v>0.1125611387395127</v>
       </c>
       <c r="C54">
-        <v>2.720370311719254</v>
+        <v>2.662577393437239</v>
       </c>
       <c r="D54">
-        <v>2.137890311719254</v>
+        <v>2.137357393437239</v>
       </c>
       <c r="E54">
-        <v>2.91152</v>
+        <v>2.96878</v>
       </c>
       <c r="F54">
-        <v>2.97752</v>
+        <v>3.03478</v>
       </c>
       <c r="G54">
         <v>3.56</v>
@@ -5834,28 +5834,28 @@
         <v>0.488</v>
       </c>
       <c r="M54">
-        <v>0.225696016</v>
+        <v>0.230036324</v>
       </c>
       <c r="N54">
-        <v>0.262303984</v>
+        <v>0.257963676</v>
       </c>
       <c r="O54">
-        <v>0.0524607968</v>
+        <v>0.0515927352</v>
       </c>
       <c r="P54">
-        <v>0.2098431872</v>
+        <v>0.2063709408</v>
       </c>
       <c r="Q54">
-        <v>0.2958431872</v>
+        <v>0.2923709407999999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1687743687327633</v>
+        <v>0.17111050795641</v>
       </c>
       <c r="T54">
-        <v>1.902374373759981</v>
+        <v>1.938513704568491</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5872,7 +5872,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.162200328782055</v>
+        <v>2.121404096163526</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5880,22 +5880,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1125611387395127</v>
+        <v>0.112577780487299</v>
       </c>
       <c r="C55">
-        <v>2.662577393437239</v>
+        <v>2.604784740773264</v>
       </c>
       <c r="D55">
-        <v>2.137357393437239</v>
+        <v>2.136824740773265</v>
       </c>
       <c r="E55">
-        <v>2.96878</v>
+        <v>3.026040000000001</v>
       </c>
       <c r="F55">
-        <v>3.03478</v>
+        <v>3.09204</v>
       </c>
       <c r="G55">
         <v>3.56</v>
@@ -5916,28 +5916,28 @@
         <v>0.488</v>
       </c>
       <c r="M55">
-        <v>0.230036324</v>
+        <v>0.2343766320000001</v>
       </c>
       <c r="N55">
-        <v>0.257963676</v>
+        <v>0.253623368</v>
       </c>
       <c r="O55">
-        <v>0.0515927352</v>
+        <v>0.05072467359999999</v>
       </c>
       <c r="P55">
-        <v>0.2063709408</v>
+        <v>0.2028986944</v>
       </c>
       <c r="Q55">
-        <v>0.2923709407999999</v>
+        <v>0.2888986943999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.17111050795641</v>
+        <v>0.17354821845065</v>
       </c>
       <c r="T55">
-        <v>1.938513704568491</v>
+        <v>1.976224310629545</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5954,7 +5954,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.121404096163526</v>
+        <v>2.08211883512346</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5962,22 +5962,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.112577780487299</v>
+        <v>0.1125944222350854</v>
       </c>
       <c r="C56">
-        <v>2.604784740773264</v>
+        <v>2.546992353528797</v>
       </c>
       <c r="D56">
-        <v>2.136824740773265</v>
+        <v>2.136292353528797</v>
       </c>
       <c r="E56">
-        <v>3.026040000000001</v>
+        <v>3.0833</v>
       </c>
       <c r="F56">
-        <v>3.09204</v>
+        <v>3.1493</v>
       </c>
       <c r="G56">
         <v>3.56</v>
@@ -5998,28 +5998,28 @@
         <v>0.488</v>
       </c>
       <c r="M56">
-        <v>0.2343766320000001</v>
+        <v>0.23871694</v>
       </c>
       <c r="N56">
-        <v>0.253623368</v>
+        <v>0.2492830599999999</v>
       </c>
       <c r="O56">
-        <v>0.05072467359999999</v>
+        <v>0.04985661199999999</v>
       </c>
       <c r="P56">
-        <v>0.2028986944</v>
+        <v>0.199426448</v>
       </c>
       <c r="Q56">
-        <v>0.2888986943999999</v>
+        <v>0.2854264479999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.17354821845065</v>
+        <v>0.176094271633523</v>
       </c>
       <c r="T56">
-        <v>1.976224310629545</v>
+        <v>2.015610943626646</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -6036,7 +6036,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.08211883512346</v>
+        <v>2.044262129030306</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6044,22 +6044,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1125944222350854</v>
+        <v>0.1126110639828717</v>
       </c>
       <c r="C57">
-        <v>2.546992353528797</v>
+        <v>2.489200231505499</v>
       </c>
       <c r="D57">
-        <v>2.136292353528797</v>
+        <v>2.135760231505499</v>
       </c>
       <c r="E57">
-        <v>3.0833</v>
+        <v>3.14056</v>
       </c>
       <c r="F57">
-        <v>3.1493</v>
+        <v>3.20656</v>
       </c>
       <c r="G57">
         <v>3.56</v>
@@ -6080,28 +6080,28 @@
         <v>0.488</v>
       </c>
       <c r="M57">
-        <v>0.23871694</v>
+        <v>0.243057248</v>
       </c>
       <c r="N57">
-        <v>0.2492830599999999</v>
+        <v>0.244942752</v>
       </c>
       <c r="O57">
-        <v>0.04985661199999999</v>
+        <v>0.0489885504</v>
       </c>
       <c r="P57">
-        <v>0.199426448</v>
+        <v>0.1959542016</v>
       </c>
       <c r="Q57">
-        <v>0.2854264479999999</v>
+        <v>0.2819542016</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.176094271633523</v>
+        <v>0.1787560545065265</v>
       </c>
       <c r="T57">
-        <v>2.015610943626646</v>
+        <v>2.056787878123616</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -6118,7 +6118,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.044262129030306</v>
+        <v>2.007757448154766</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6126,22 +6126,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1126110639828717</v>
+        <v>0.119102905730658</v>
       </c>
       <c r="C58">
-        <v>2.489200231505499</v>
+        <v>2.242793330766061</v>
       </c>
       <c r="D58">
-        <v>2.135760231505499</v>
+        <v>1.946613330766061</v>
       </c>
       <c r="E58">
-        <v>3.14056</v>
+        <v>3.197820000000001</v>
       </c>
       <c r="F58">
-        <v>3.20656</v>
+        <v>3.26382</v>
       </c>
       <c r="G58">
         <v>3.56</v>
@@ -6162,45 +6162,45 @@
         <v>0.488</v>
       </c>
       <c r="M58">
-        <v>0.243057248</v>
+        <v>0.2937438</v>
       </c>
       <c r="N58">
-        <v>0.244942752</v>
+        <v>0.1942562</v>
       </c>
       <c r="O58">
-        <v>0.0489885504</v>
+        <v>0.03885124</v>
       </c>
       <c r="P58">
-        <v>0.1959542016</v>
+        <v>0.15540496</v>
       </c>
       <c r="Q58">
-        <v>0.2819542016</v>
+        <v>0.2414049599999999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1787560545065265</v>
+        <v>0.1815416412340884</v>
       </c>
       <c r="T58">
-        <v>2.056787878123616</v>
+        <v>2.099880018876258</v>
       </c>
       <c r="U58">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V58">
         <v>0.2</v>
       </c>
       <c r="W58">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y58">
-        <v>2.007757448154766</v>
+        <v>1.661311660024824</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6208,22 +6208,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.119102905730658</v>
+        <v>0.1192331474784443</v>
       </c>
       <c r="C59">
-        <v>2.242793330766061</v>
+        <v>2.182080798344819</v>
       </c>
       <c r="D59">
-        <v>1.946613330766061</v>
+        <v>1.943160798344819</v>
       </c>
       <c r="E59">
-        <v>3.197820000000001</v>
+        <v>3.25508</v>
       </c>
       <c r="F59">
-        <v>3.26382</v>
+        <v>3.32108</v>
       </c>
       <c r="G59">
         <v>3.56</v>
@@ -6244,28 +6244,28 @@
         <v>0.488</v>
       </c>
       <c r="M59">
-        <v>0.2937438</v>
+        <v>0.2988972</v>
       </c>
       <c r="N59">
-        <v>0.1942562</v>
+        <v>0.1891028</v>
       </c>
       <c r="O59">
-        <v>0.03885124</v>
+        <v>0.03782056</v>
       </c>
       <c r="P59">
-        <v>0.15540496</v>
+        <v>0.15128224</v>
       </c>
       <c r="Q59">
-        <v>0.2414049599999999</v>
+        <v>0.2372822399999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1815416412340884</v>
+        <v>0.184459874948677</v>
       </c>
       <c r="T59">
-        <v>2.099880018876258</v>
+        <v>2.145024166331407</v>
       </c>
       <c r="U59">
         <v>0.09</v>
@@ -6282,7 +6282,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.661311660024824</v>
+        <v>1.632668355541638</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6290,22 +6290,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1192331474784443</v>
+        <v>0.1193633892262306</v>
       </c>
       <c r="C60">
-        <v>2.18208079834482</v>
+        <v>2.121380491131296</v>
       </c>
       <c r="D60">
-        <v>1.94316079834482</v>
+        <v>1.939720491131295</v>
       </c>
       <c r="E60">
-        <v>3.25508</v>
+        <v>3.31234</v>
       </c>
       <c r="F60">
-        <v>3.32108</v>
+        <v>3.37834</v>
       </c>
       <c r="G60">
         <v>3.56</v>
@@ -6326,28 +6326,28 @@
         <v>0.488</v>
       </c>
       <c r="M60">
-        <v>0.2988972</v>
+        <v>0.3040505999999999</v>
       </c>
       <c r="N60">
-        <v>0.1891028</v>
+        <v>0.1839494</v>
       </c>
       <c r="O60">
-        <v>0.03782056</v>
+        <v>0.03678988000000001</v>
       </c>
       <c r="P60">
-        <v>0.15128224</v>
+        <v>0.14715952</v>
       </c>
       <c r="Q60">
-        <v>0.23728224</v>
+        <v>0.23315952</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1844598749486769</v>
+        <v>0.1875204615273918</v>
       </c>
       <c r="T60">
-        <v>2.145024166331406</v>
+        <v>2.192370467320953</v>
       </c>
       <c r="U60">
         <v>0.09</v>
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.632668355541638</v>
+        <v>1.604996010532458</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6372,22 +6372,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1193633892262306</v>
+        <v>0.119493630974017</v>
       </c>
       <c r="C61">
-        <v>2.121380491131296</v>
+        <v>2.060692344307169</v>
       </c>
       <c r="D61">
-        <v>1.939720491131295</v>
+        <v>1.936292344307169</v>
       </c>
       <c r="E61">
-        <v>3.31234</v>
+        <v>3.3696</v>
       </c>
       <c r="F61">
-        <v>3.37834</v>
+        <v>3.4356</v>
       </c>
       <c r="G61">
         <v>3.56</v>
@@ -6408,28 +6408,28 @@
         <v>0.488</v>
       </c>
       <c r="M61">
-        <v>0.3040505999999999</v>
+        <v>0.309204</v>
       </c>
       <c r="N61">
-        <v>0.1839494</v>
+        <v>0.178796</v>
       </c>
       <c r="O61">
-        <v>0.03678988000000001</v>
+        <v>0.0357592</v>
       </c>
       <c r="P61">
-        <v>0.14715952</v>
+        <v>0.1430368</v>
       </c>
       <c r="Q61">
-        <v>0.23315952</v>
+        <v>0.2290368</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1875204615273918</v>
+        <v>0.1907340774350424</v>
       </c>
       <c r="T61">
-        <v>2.192370467320953</v>
+        <v>2.242084083359977</v>
       </c>
       <c r="U61">
         <v>0.09</v>
@@ -6446,7 +6446,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.604996010532458</v>
+        <v>1.578246077023583</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6454,22 +6454,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.119493630974017</v>
+        <v>0.1196238727218033</v>
       </c>
       <c r="C62">
-        <v>2.060692344307169</v>
+        <v>2.000016293511538</v>
       </c>
       <c r="D62">
-        <v>1.936292344307169</v>
+        <v>1.932876293511538</v>
       </c>
       <c r="E62">
-        <v>3.3696</v>
+        <v>3.42686</v>
       </c>
       <c r="F62">
-        <v>3.4356</v>
+        <v>3.49286</v>
       </c>
       <c r="G62">
         <v>3.56</v>
@@ -6490,28 +6490,28 @@
         <v>0.488</v>
       </c>
       <c r="M62">
-        <v>0.309204</v>
+        <v>0.3143574</v>
       </c>
       <c r="N62">
-        <v>0.178796</v>
+        <v>0.1736426</v>
       </c>
       <c r="O62">
-        <v>0.0357592</v>
+        <v>0.03472852000000001</v>
       </c>
       <c r="P62">
-        <v>0.1430368</v>
+        <v>0.13891408</v>
       </c>
       <c r="Q62">
-        <v>0.2290368</v>
+        <v>0.22491408</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1907340774350424</v>
+        <v>0.19411249415847</v>
       </c>
       <c r="T62">
-        <v>2.242084083359977</v>
+        <v>2.29434711560613</v>
       </c>
       <c r="U62">
         <v>0.09</v>
@@ -6528,7 +6528,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.578246077023583</v>
+        <v>1.552373190515</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6536,22 +6536,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1196238727218033</v>
+        <v>0.1197541144695896</v>
       </c>
       <c r="C63">
-        <v>2.000016293511538</v>
+        <v>1.939352274836888</v>
       </c>
       <c r="D63">
-        <v>1.932876293511538</v>
+        <v>1.929472274836888</v>
       </c>
       <c r="E63">
-        <v>3.42686</v>
+        <v>3.48412</v>
       </c>
       <c r="F63">
-        <v>3.49286</v>
+        <v>3.55012</v>
       </c>
       <c r="G63">
         <v>3.56</v>
@@ -6572,28 +6572,28 @@
         <v>0.488</v>
       </c>
       <c r="M63">
-        <v>0.3143574</v>
+        <v>0.3195108</v>
       </c>
       <c r="N63">
-        <v>0.1736426</v>
+        <v>0.1684892</v>
       </c>
       <c r="O63">
-        <v>0.03472852000000001</v>
+        <v>0.03369784</v>
       </c>
       <c r="P63">
-        <v>0.13891408</v>
+        <v>0.13479136</v>
       </c>
       <c r="Q63">
-        <v>0.22491408</v>
+        <v>0.22079136</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.19411249415847</v>
+        <v>0.1976687222883937</v>
       </c>
       <c r="T63">
-        <v>2.29434711560613</v>
+        <v>2.349360833759976</v>
       </c>
       <c r="U63">
         <v>0.09</v>
@@ -6610,7 +6610,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.552373190515</v>
+        <v>1.527334913248629</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6618,22 +6618,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1197541144695896</v>
+        <v>0.1198843562173759</v>
       </c>
       <c r="C64">
-        <v>1.939352274836888</v>
+        <v>1.878700224825106</v>
       </c>
       <c r="D64">
-        <v>1.929472274836888</v>
+        <v>1.926080224825106</v>
       </c>
       <c r="E64">
-        <v>3.48412</v>
+        <v>3.54138</v>
       </c>
       <c r="F64">
-        <v>3.55012</v>
+        <v>3.60738</v>
       </c>
       <c r="G64">
         <v>3.56</v>
@@ -6654,28 +6654,28 @@
         <v>0.488</v>
       </c>
       <c r="M64">
-        <v>0.3195108</v>
+        <v>0.3246642</v>
       </c>
       <c r="N64">
-        <v>0.1684892</v>
+        <v>0.1633358</v>
       </c>
       <c r="O64">
-        <v>0.03369784</v>
+        <v>0.03266715999999999</v>
       </c>
       <c r="P64">
-        <v>0.13479136</v>
+        <v>0.13066864</v>
       </c>
       <c r="Q64">
-        <v>0.22079136</v>
+        <v>0.2166686399999999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1976687222883937</v>
+        <v>0.201417178965881</v>
       </c>
       <c r="T64">
-        <v>2.349360833759976</v>
+        <v>2.407348266408624</v>
       </c>
       <c r="U64">
         <v>0.09</v>
@@ -6692,7 +6692,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.527334913248629</v>
+        <v>1.503091501927222</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6700,22 +6700,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1198843562173759</v>
+        <v>0.1516247939434619</v>
       </c>
       <c r="C65">
-        <v>1.878700224825106</v>
+        <v>1.243743570256907</v>
       </c>
       <c r="D65">
-        <v>1.926080224825106</v>
+        <v>1.348383570256907</v>
       </c>
       <c r="E65">
-        <v>3.54138</v>
+        <v>3.59864</v>
       </c>
       <c r="F65">
-        <v>3.60738</v>
+        <v>3.66464</v>
       </c>
       <c r="G65">
         <v>3.56</v>
@@ -6736,45 +6736,45 @@
         <v>0.488</v>
       </c>
       <c r="M65">
-        <v>0.3246642</v>
+        <v>0.5379691520000001</v>
       </c>
       <c r="N65">
-        <v>0.1633358</v>
+        <v>-0.04996915200000007</v>
       </c>
       <c r="O65">
-        <v>0.03266715999999999</v>
+        <v>-0.009993830400000014</v>
       </c>
       <c r="P65">
-        <v>0.13066864</v>
+        <v>-0.03997532160000006</v>
       </c>
       <c r="Q65">
-        <v>0.2166686399999999</v>
+        <v>0.04602467839999991</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.201417178965881</v>
+        <v>0.2075495877092127</v>
       </c>
       <c r="T65">
-        <v>2.407348266408624</v>
+        <v>2.502214679328277</v>
       </c>
       <c r="U65">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.2</v>
+        <v>0.1814230418921864</v>
       </c>
       <c r="W65">
-        <v>0.07199999999999999</v>
+        <v>0.1201670974502271</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y65">
-        <v>1.503091501927222</v>
+        <v>0.9071152094609319</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6782,22 +6782,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1516247939434619</v>
+        <v>0.1526347939434619</v>
       </c>
       <c r="C66">
-        <v>1.243743570256907</v>
+        <v>1.173736155714411</v>
       </c>
       <c r="D66">
-        <v>1.348383570256907</v>
+        <v>1.335636155714412</v>
       </c>
       <c r="E66">
-        <v>3.59864</v>
+        <v>3.6559</v>
       </c>
       <c r="F66">
-        <v>3.66464</v>
+        <v>3.7219</v>
       </c>
       <c r="G66">
         <v>3.56</v>
@@ -6818,37 +6818,37 @@
         <v>0.488</v>
       </c>
       <c r="M66">
-        <v>0.5379691520000001</v>
+        <v>0.5463749200000001</v>
       </c>
       <c r="N66">
-        <v>-0.04996915200000007</v>
+        <v>-0.05837492000000011</v>
       </c>
       <c r="O66">
-        <v>-0.009993830400000014</v>
+        <v>-0.01167498400000002</v>
       </c>
       <c r="P66">
-        <v>-0.03997532160000006</v>
+        <v>-0.04669993600000009</v>
       </c>
       <c r="Q66">
-        <v>0.04602467839999991</v>
+        <v>0.03930006399999988</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2075495877092127</v>
+        <v>0.2121710045009045</v>
       </c>
       <c r="T66">
-        <v>2.502214679328277</v>
+        <v>2.573706527309085</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.1814230418921864</v>
+        <v>0.1786319181707682</v>
       </c>
       <c r="W66">
-        <v>0.1201670974502271</v>
+        <v>0.1205768344125312</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.9071152094609319</v>
+        <v>0.8931595908538407</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6864,22 +6864,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1526347939434619</v>
+        <v>0.1536447939434619</v>
       </c>
       <c r="C67">
-        <v>1.173736155714411</v>
+        <v>1.103967508166911</v>
       </c>
       <c r="D67">
-        <v>1.335636155714412</v>
+        <v>1.323127508166911</v>
       </c>
       <c r="E67">
-        <v>3.6559</v>
+        <v>3.71316</v>
       </c>
       <c r="F67">
-        <v>3.7219</v>
+        <v>3.77916</v>
       </c>
       <c r="G67">
         <v>3.56</v>
@@ -6900,37 +6900,37 @@
         <v>0.488</v>
       </c>
       <c r="M67">
-        <v>0.5463749200000001</v>
+        <v>0.554780688</v>
       </c>
       <c r="N67">
-        <v>-0.05837492000000011</v>
+        <v>-0.06678068800000003</v>
       </c>
       <c r="O67">
-        <v>-0.01167498400000002</v>
+        <v>-0.01335613760000001</v>
       </c>
       <c r="P67">
-        <v>-0.04669993600000009</v>
+        <v>-0.05342455040000003</v>
       </c>
       <c r="Q67">
-        <v>0.03930006399999988</v>
+        <v>0.03257544959999994</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2121710045009045</v>
+        <v>0.2170642693391663</v>
       </c>
       <c r="T67">
-        <v>2.573706527309085</v>
+        <v>2.649403778112293</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.1786319181707682</v>
+        <v>0.1759253739560596</v>
       </c>
       <c r="W67">
-        <v>0.1205768344125312</v>
+        <v>0.1209741551032505</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8931595908538407</v>
+        <v>0.8796268697802977</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6946,22 +6946,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1536447939434619</v>
+        <v>0.1546547939434619</v>
       </c>
       <c r="C68">
-        <v>1.103967508166911</v>
+        <v>1.034430981476294</v>
       </c>
       <c r="D68">
-        <v>1.323127508166911</v>
+        <v>1.310850981476294</v>
       </c>
       <c r="E68">
-        <v>3.71316</v>
+        <v>3.770420000000001</v>
       </c>
       <c r="F68">
-        <v>3.77916</v>
+        <v>3.83642</v>
       </c>
       <c r="G68">
         <v>3.56</v>
@@ -6982,37 +6982,37 @@
         <v>0.488</v>
       </c>
       <c r="M68">
-        <v>0.554780688</v>
+        <v>0.5631864560000001</v>
       </c>
       <c r="N68">
-        <v>-0.06678068800000003</v>
+        <v>-0.07518645600000007</v>
       </c>
       <c r="O68">
-        <v>-0.01335613760000001</v>
+        <v>-0.01503729120000001</v>
       </c>
       <c r="P68">
-        <v>-0.05342455040000003</v>
+        <v>-0.06014916480000006</v>
       </c>
       <c r="Q68">
-        <v>0.03257544959999994</v>
+        <v>0.02585083519999991</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2170642693391663</v>
+        <v>0.2222540956827775</v>
       </c>
       <c r="T68">
-        <v>2.649403778112293</v>
+        <v>2.729688741085393</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.1759253739560596</v>
+        <v>0.1732996221059691</v>
       </c>
       <c r="W68">
-        <v>0.1209741551032505</v>
+        <v>0.1213596154748438</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8796268697802977</v>
+        <v>0.8664981105298455</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7028,22 +7028,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1546547939434619</v>
+        <v>0.1556647939434619</v>
       </c>
       <c r="C69">
-        <v>1.034430981476294</v>
+        <v>0.9651201738993698</v>
       </c>
       <c r="D69">
-        <v>1.310850981476294</v>
+        <v>1.29880017389937</v>
       </c>
       <c r="E69">
-        <v>3.770420000000001</v>
+        <v>3.82768</v>
       </c>
       <c r="F69">
-        <v>3.83642</v>
+        <v>3.89368</v>
       </c>
       <c r="G69">
         <v>3.56</v>
@@ -7064,37 +7064,37 @@
         <v>0.488</v>
       </c>
       <c r="M69">
-        <v>0.5631864560000001</v>
+        <v>0.5715922240000001</v>
       </c>
       <c r="N69">
-        <v>-0.07518645600000007</v>
+        <v>-0.0835922240000001</v>
       </c>
       <c r="O69">
-        <v>-0.01503729120000001</v>
+        <v>-0.01671844480000002</v>
       </c>
       <c r="P69">
-        <v>-0.06014916480000006</v>
+        <v>-0.06687377920000008</v>
       </c>
       <c r="Q69">
-        <v>0.02585083519999991</v>
+        <v>0.01912622079999989</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2222540956827775</v>
+        <v>0.2277682861728643</v>
       </c>
       <c r="T69">
-        <v>2.729688741085393</v>
+        <v>2.814991514244312</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.1732996221059691</v>
+        <v>0.1707510982514695</v>
       </c>
       <c r="W69">
-        <v>0.1213596154748438</v>
+        <v>0.1217337387766843</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8664981105298455</v>
+        <v>0.8537554912573477</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7110,22 +7110,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1556647939434619</v>
+        <v>0.1566747939434619</v>
       </c>
       <c r="C70">
-        <v>0.9651201738993698</v>
+        <v>0.8960289169564506</v>
       </c>
       <c r="D70">
-        <v>1.29880017389937</v>
+        <v>1.28696891695645</v>
       </c>
       <c r="E70">
-        <v>3.82768</v>
+        <v>3.88494</v>
       </c>
       <c r="F70">
-        <v>3.89368</v>
+        <v>3.95094</v>
       </c>
       <c r="G70">
         <v>3.56</v>
@@ -7146,37 +7146,37 @@
         <v>0.488</v>
       </c>
       <c r="M70">
-        <v>0.5715922240000001</v>
+        <v>0.579997992</v>
       </c>
       <c r="N70">
-        <v>-0.0835922240000001</v>
+        <v>-0.09199799200000003</v>
       </c>
       <c r="O70">
-        <v>-0.01671844480000002</v>
+        <v>-0.0183995984</v>
       </c>
       <c r="P70">
-        <v>-0.06687377920000008</v>
+        <v>-0.07359839360000002</v>
       </c>
       <c r="Q70">
-        <v>0.01912622079999989</v>
+        <v>0.01240160639999995</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2277682861728643</v>
+        <v>0.233638230888118</v>
       </c>
       <c r="T70">
-        <v>2.814991514244312</v>
+        <v>2.905797692123161</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.1707510982514695</v>
+        <v>0.1682764446536222</v>
       </c>
       <c r="W70">
-        <v>0.1217337387766843</v>
+        <v>0.1220970179248483</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8537554912573477</v>
+        <v>0.8413822232681109</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7192,22 +7192,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1566747939434619</v>
+        <v>0.1576847939434619</v>
       </c>
       <c r="C71">
-        <v>0.8960289169564506</v>
+        <v>0.827151264902831</v>
       </c>
       <c r="D71">
-        <v>1.28696891695645</v>
+        <v>1.275351264902831</v>
       </c>
       <c r="E71">
-        <v>3.88494</v>
+        <v>3.942200000000001</v>
       </c>
       <c r="F71">
-        <v>3.95094</v>
+        <v>4.0082</v>
       </c>
       <c r="G71">
         <v>3.56</v>
@@ -7228,37 +7228,37 @@
         <v>0.488</v>
       </c>
       <c r="M71">
-        <v>0.579997992</v>
+        <v>0.5884037600000002</v>
       </c>
       <c r="N71">
-        <v>-0.09199799200000003</v>
+        <v>-0.1004037600000002</v>
       </c>
       <c r="O71">
-        <v>-0.0183995984</v>
+        <v>-0.02008075200000004</v>
       </c>
       <c r="P71">
-        <v>-0.07359839360000002</v>
+        <v>-0.08032300800000014</v>
       </c>
       <c r="Q71">
-        <v>0.01240160639999995</v>
+        <v>0.005676991999999825</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.233638230888118</v>
+        <v>0.2398995052510552</v>
       </c>
       <c r="T71">
-        <v>2.905797692123161</v>
+        <v>3.002657615193932</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.1682764446536222</v>
+        <v>0.1658724954442847</v>
       </c>
       <c r="W71">
-        <v>0.1220970179248483</v>
+        <v>0.122449917668779</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8413822232681109</v>
+        <v>0.8293624772214233</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7274,22 +7274,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1576847939434619</v>
+        <v>0.1586947939434619</v>
       </c>
       <c r="C72">
-        <v>0.827151264902831</v>
+        <v>0.7584814847654311</v>
       </c>
       <c r="D72">
-        <v>1.275351264902831</v>
+        <v>1.263941484765432</v>
       </c>
       <c r="E72">
-        <v>3.942200000000001</v>
+        <v>3.999460000000001</v>
       </c>
       <c r="F72">
-        <v>4.0082</v>
+        <v>4.065460000000001</v>
       </c>
       <c r="G72">
         <v>3.56</v>
@@ -7310,37 +7310,37 @@
         <v>0.488</v>
       </c>
       <c r="M72">
-        <v>0.5884037600000002</v>
+        <v>0.5968095280000002</v>
       </c>
       <c r="N72">
-        <v>-0.1004037600000002</v>
+        <v>-0.1088095280000002</v>
       </c>
       <c r="O72">
-        <v>-0.02008075200000004</v>
+        <v>-0.02176190560000004</v>
       </c>
       <c r="P72">
-        <v>-0.08032300800000014</v>
+        <v>-0.08704762240000016</v>
       </c>
       <c r="Q72">
-        <v>0.005676991999999825</v>
+        <v>-0.001047622400000198</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2398995052510552</v>
+        <v>0.2465925916390227</v>
       </c>
       <c r="T72">
-        <v>3.002657615193932</v>
+        <v>3.106197532959241</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.1658724954442847</v>
+        <v>0.1635362631140835</v>
       </c>
       <c r="W72">
-        <v>0.122449917668779</v>
+        <v>0.1227928765748525</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8293624772214233</v>
+        <v>0.8176813155704173</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7356,22 +7356,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1586947939434619</v>
+        <v>0.1597047939434619</v>
       </c>
       <c r="C73">
-        <v>0.758481484765432</v>
+        <v>0.6900140469095088</v>
       </c>
       <c r="D73">
-        <v>1.263941484765432</v>
+        <v>1.252734046909509</v>
       </c>
       <c r="E73">
-        <v>3.99946</v>
+        <v>4.05672</v>
       </c>
       <c r="F73">
-        <v>4.06546</v>
+        <v>4.12272</v>
       </c>
       <c r="G73">
         <v>3.56</v>
@@ -7392,37 +7392,37 @@
         <v>0.488</v>
       </c>
       <c r="M73">
-        <v>0.5968095280000001</v>
+        <v>0.6052152960000001</v>
       </c>
       <c r="N73">
-        <v>-0.1088095280000001</v>
+        <v>-0.1172152960000001</v>
       </c>
       <c r="O73">
-        <v>-0.02176190560000002</v>
+        <v>-0.02344305920000003</v>
       </c>
       <c r="P73">
-        <v>-0.08704762240000008</v>
+        <v>-0.0937722368000001</v>
       </c>
       <c r="Q73">
-        <v>-0.001047622400000114</v>
+        <v>-0.007772236800000137</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2465925916390226</v>
+        <v>0.2537637556261306</v>
       </c>
       <c r="T73">
-        <v>3.10619753295924</v>
+        <v>3.217133159136356</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.1635362631140835</v>
+        <v>0.1612649261263879</v>
       </c>
       <c r="W73">
-        <v>0.1227928765748525</v>
+        <v>0.1231263088446463</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8176813155704175</v>
+        <v>0.8063246306319394</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7438,22 +7438,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1597047939434619</v>
+        <v>0.2021918697636916</v>
       </c>
       <c r="C74">
-        <v>0.6900140469095088</v>
+        <v>0.2924230149060518</v>
       </c>
       <c r="D74">
-        <v>1.252734046909509</v>
+        <v>0.9124030149060512</v>
       </c>
       <c r="E74">
-        <v>4.05672</v>
+        <v>4.11398</v>
       </c>
       <c r="F74">
-        <v>4.12272</v>
+        <v>4.17998</v>
       </c>
       <c r="G74">
         <v>3.56</v>
@@ -7474,45 +7474,45 @@
         <v>0.488</v>
       </c>
       <c r="M74">
-        <v>0.6052152960000001</v>
+        <v>0.839339984</v>
       </c>
       <c r="N74">
-        <v>-0.1172152960000001</v>
+        <v>-0.351339984</v>
       </c>
       <c r="O74">
-        <v>-0.02344305920000003</v>
+        <v>-0.0702679968</v>
       </c>
       <c r="P74">
-        <v>-0.0937722368000001</v>
+        <v>-0.2810719872</v>
       </c>
       <c r="Q74">
-        <v>-0.007772236800000137</v>
+        <v>-0.1950719872</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2537637556261306</v>
+        <v>0.269084916279801</v>
       </c>
       <c r="T74">
-        <v>3.217133159136356</v>
+        <v>3.454146641735653</v>
       </c>
       <c r="U74">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1612649261263879</v>
+        <v>0.1162818427103551</v>
       </c>
       <c r="W74">
-        <v>0.1231263088446463</v>
+        <v>0.1774506059837607</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y74">
-        <v>0.8063246306319394</v>
+        <v>0.5814092135517757</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7520,22 +7520,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2021918697636916</v>
+        <v>0.2037418697636916</v>
       </c>
       <c r="C75">
-        <v>0.2924230149060518</v>
+        <v>0.2262089315130895</v>
       </c>
       <c r="D75">
-        <v>0.9124030149060512</v>
+        <v>0.9034489315130894</v>
       </c>
       <c r="E75">
-        <v>4.11398</v>
+        <v>4.17124</v>
       </c>
       <c r="F75">
-        <v>4.17998</v>
+        <v>4.23724</v>
       </c>
       <c r="G75">
         <v>3.56</v>
@@ -7556,37 +7556,37 @@
         <v>0.488</v>
       </c>
       <c r="M75">
-        <v>0.839339984</v>
+        <v>0.850837792</v>
       </c>
       <c r="N75">
-        <v>-0.351339984</v>
+        <v>-0.362837792</v>
       </c>
       <c r="O75">
-        <v>-0.0702679968</v>
+        <v>-0.0725675584</v>
       </c>
       <c r="P75">
-        <v>-0.2810719872</v>
+        <v>-0.2902702336</v>
       </c>
       <c r="Q75">
-        <v>-0.1950719872</v>
+        <v>-0.2042702336</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.269084916279801</v>
+        <v>0.277672797675178</v>
       </c>
       <c r="T75">
-        <v>3.454146641735653</v>
+        <v>3.586998435648563</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1162818427103551</v>
+        <v>0.1147104664575125</v>
       </c>
       <c r="W75">
-        <v>0.1774506059837607</v>
+        <v>0.1777661383353315</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5814092135517757</v>
+        <v>0.5735523322875625</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7602,22 +7602,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2037418697636916</v>
+        <v>0.2052918697636916</v>
       </c>
       <c r="C76">
-        <v>0.2262089315130895</v>
+        <v>0.1601688861984281</v>
       </c>
       <c r="D76">
-        <v>0.9034489315130894</v>
+        <v>0.8946688861984282</v>
       </c>
       <c r="E76">
-        <v>4.17124</v>
+        <v>4.2285</v>
       </c>
       <c r="F76">
-        <v>4.23724</v>
+        <v>4.2945</v>
       </c>
       <c r="G76">
         <v>3.56</v>
@@ -7638,37 +7638,37 @@
         <v>0.488</v>
       </c>
       <c r="M76">
-        <v>0.850837792</v>
+        <v>0.8623356000000001</v>
       </c>
       <c r="N76">
-        <v>-0.362837792</v>
+        <v>-0.3743356000000001</v>
       </c>
       <c r="O76">
-        <v>-0.0725675584</v>
+        <v>-0.07486712000000002</v>
       </c>
       <c r="P76">
-        <v>-0.2902702336</v>
+        <v>-0.2994684800000001</v>
       </c>
       <c r="Q76">
-        <v>-0.2042702336</v>
+        <v>-0.2134684800000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.277672797675178</v>
+        <v>0.2869477095821851</v>
       </c>
       <c r="T76">
-        <v>3.586998435648563</v>
+        <v>3.730478373074506</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1147104664575125</v>
+        <v>0.1131809935714123</v>
       </c>
       <c r="W76">
-        <v>0.1777661383353315</v>
+        <v>0.1780732564908604</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5735523322875625</v>
+        <v>0.5659049678570616</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7684,22 +7684,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2052918697636916</v>
+        <v>0.2068418697636916</v>
       </c>
       <c r="C77">
-        <v>0.1601688861984281</v>
+        <v>0.09429785370332411</v>
       </c>
       <c r="D77">
-        <v>0.8946688861984282</v>
+        <v>0.8860578537033235</v>
       </c>
       <c r="E77">
-        <v>4.2285</v>
+        <v>4.28576</v>
       </c>
       <c r="F77">
-        <v>4.2945</v>
+        <v>4.35176</v>
       </c>
       <c r="G77">
         <v>3.56</v>
@@ -7720,37 +7720,37 @@
         <v>0.488</v>
       </c>
       <c r="M77">
-        <v>0.8623356000000001</v>
+        <v>0.873833408</v>
       </c>
       <c r="N77">
-        <v>-0.3743356000000001</v>
+        <v>-0.385833408</v>
       </c>
       <c r="O77">
-        <v>-0.07486712000000002</v>
+        <v>-0.07716668160000001</v>
       </c>
       <c r="P77">
-        <v>-0.2994684800000001</v>
+        <v>-0.3086667264</v>
       </c>
       <c r="Q77">
-        <v>-0.2134684800000001</v>
+        <v>-0.2226667264</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2869477095821851</v>
+        <v>0.2969955308147762</v>
       </c>
       <c r="T77">
-        <v>3.730478373074506</v>
+        <v>3.88591497195261</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1131809935714123</v>
+        <v>0.1116917699717885</v>
       </c>
       <c r="W77">
-        <v>0.1780732564908604</v>
+        <v>0.1783722925896649</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5659049678570616</v>
+        <v>0.5584588498589425</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7766,22 +7766,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2068418697636916</v>
+        <v>0.2083918697636916</v>
       </c>
       <c r="C78">
-        <v>0.09429785370332411</v>
+        <v>0.02859100039364559</v>
       </c>
       <c r="D78">
-        <v>0.8860578537033235</v>
+        <v>0.8776110003936454</v>
       </c>
       <c r="E78">
-        <v>4.28576</v>
+        <v>4.34302</v>
       </c>
       <c r="F78">
-        <v>4.35176</v>
+        <v>4.40902</v>
       </c>
       <c r="G78">
         <v>3.56</v>
@@ -7802,37 +7802,37 @@
         <v>0.488</v>
       </c>
       <c r="M78">
-        <v>0.873833408</v>
+        <v>0.885331216</v>
       </c>
       <c r="N78">
-        <v>-0.385833408</v>
+        <v>-0.397331216</v>
       </c>
       <c r="O78">
-        <v>-0.07716668160000001</v>
+        <v>-0.07946624320000001</v>
       </c>
       <c r="P78">
-        <v>-0.3086667264</v>
+        <v>-0.3178649728</v>
       </c>
       <c r="Q78">
-        <v>-0.2226667264</v>
+        <v>-0.2318649728</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2969955308147762</v>
+        <v>0.30791707563281</v>
       </c>
       <c r="T78">
-        <v>3.88591497195261</v>
+        <v>4.054867796820115</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.1116917699717885</v>
+        <v>0.1102412275046224</v>
       </c>
       <c r="W78">
-        <v>0.1783722925896649</v>
+        <v>0.1786635615170718</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5584588498589425</v>
+        <v>0.5512061375231121</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7848,22 +7848,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2083918697636916</v>
+        <v>0.2099418697636916</v>
       </c>
       <c r="C79">
-        <v>0.02859100039364559</v>
+        <v>-0.03695632478772648</v>
       </c>
       <c r="D79">
-        <v>0.8776110003936454</v>
+        <v>0.8693236752122734</v>
       </c>
       <c r="E79">
-        <v>4.34302</v>
+        <v>4.40028</v>
       </c>
       <c r="F79">
-        <v>4.40902</v>
+        <v>4.46628</v>
       </c>
       <c r="G79">
         <v>3.56</v>
@@ -7884,37 +7884,37 @@
         <v>0.488</v>
       </c>
       <c r="M79">
-        <v>0.885331216</v>
+        <v>0.8968290240000001</v>
       </c>
       <c r="N79">
-        <v>-0.397331216</v>
+        <v>-0.4088290240000001</v>
       </c>
       <c r="O79">
-        <v>-0.07946624320000001</v>
+        <v>-0.08176580480000002</v>
       </c>
       <c r="P79">
-        <v>-0.3178649728</v>
+        <v>-0.3270632192000001</v>
       </c>
       <c r="Q79">
-        <v>-0.2318649728</v>
+        <v>-0.2410632192000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.30791707563281</v>
+        <v>0.3198314881615741</v>
       </c>
       <c r="T79">
-        <v>4.054867796820115</v>
+        <v>4.239179969402849</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1102412275046224</v>
+        <v>0.1088278784340503</v>
       </c>
       <c r="W79">
-        <v>0.1786635615170718</v>
+        <v>0.1789473620104427</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5512061375231121</v>
+        <v>0.5441393921702515</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7930,22 +7930,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2099418697636916</v>
+        <v>0.2114918697636916</v>
       </c>
       <c r="C80">
-        <v>-0.03695632478772648</v>
+        <v>-0.1023485988606838</v>
       </c>
       <c r="D80">
-        <v>0.8693236752122734</v>
+        <v>0.8611914011393164</v>
       </c>
       <c r="E80">
-        <v>4.40028</v>
+        <v>4.457540000000001</v>
       </c>
       <c r="F80">
-        <v>4.46628</v>
+        <v>4.523540000000001</v>
       </c>
       <c r="G80">
         <v>3.56</v>
@@ -7966,37 +7966,37 @@
         <v>0.488</v>
       </c>
       <c r="M80">
-        <v>0.8968290240000001</v>
+        <v>0.9083268320000002</v>
       </c>
       <c r="N80">
-        <v>-0.4088290240000001</v>
+        <v>-0.4203268320000002</v>
       </c>
       <c r="O80">
-        <v>-0.08176580480000002</v>
+        <v>-0.08406536640000005</v>
       </c>
       <c r="P80">
-        <v>-0.3270632192000001</v>
+        <v>-0.3362614656000001</v>
       </c>
       <c r="Q80">
-        <v>-0.2410632192000001</v>
+        <v>-0.2502614656000002</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3198314881615741</v>
+        <v>0.3328806066454585</v>
       </c>
       <c r="T80">
-        <v>4.239179969402849</v>
+        <v>4.441045682231556</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1088278784340503</v>
+        <v>0.1074503103526066</v>
       </c>
       <c r="W80">
-        <v>0.1789473620104427</v>
+        <v>0.1792239776811966</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5441393921702515</v>
+        <v>0.5372515517630332</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8012,22 +8012,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2114918697636916</v>
+        <v>0.2130418697636915</v>
       </c>
       <c r="C81">
-        <v>-0.1023485988606838</v>
+        <v>-0.1675901328727818</v>
       </c>
       <c r="D81">
-        <v>0.8611914011393164</v>
+        <v>0.8532098671272177</v>
       </c>
       <c r="E81">
-        <v>4.457540000000001</v>
+        <v>4.5148</v>
       </c>
       <c r="F81">
-        <v>4.523540000000001</v>
+        <v>4.5808</v>
       </c>
       <c r="G81">
         <v>3.56</v>
@@ -8048,37 +8048,37 @@
         <v>0.488</v>
       </c>
       <c r="M81">
-        <v>0.9083268320000002</v>
+        <v>0.91982464</v>
       </c>
       <c r="N81">
-        <v>-0.4203268320000002</v>
+        <v>-0.43182464</v>
       </c>
       <c r="O81">
-        <v>-0.08406536640000005</v>
+        <v>-0.08636492800000001</v>
       </c>
       <c r="P81">
-        <v>-0.3362614656000001</v>
+        <v>-0.345459712</v>
       </c>
       <c r="Q81">
-        <v>-0.2502614656000002</v>
+        <v>-0.259459712</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3328806066454585</v>
+        <v>0.3472346369777314</v>
       </c>
       <c r="T81">
-        <v>4.441045682231556</v>
+        <v>4.663097966343133</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1074503103526066</v>
+        <v>0.1061071814731991</v>
       </c>
       <c r="W81">
-        <v>0.1792239776811966</v>
+        <v>0.1794936779601816</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5372515517630332</v>
+        <v>0.5305359073659953</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8094,22 +8094,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2130418697636915</v>
+        <v>0.2145918697636916</v>
       </c>
       <c r="C82">
-        <v>-0.1675901328727818</v>
+        <v>-0.2326850795197908</v>
       </c>
       <c r="D82">
-        <v>0.8532098671272177</v>
+        <v>0.8453749204802098</v>
       </c>
       <c r="E82">
-        <v>4.5148</v>
+        <v>4.57206</v>
       </c>
       <c r="F82">
-        <v>4.5808</v>
+        <v>4.63806</v>
       </c>
       <c r="G82">
         <v>3.56</v>
@@ -8130,37 +8130,37 @@
         <v>0.488</v>
       </c>
       <c r="M82">
-        <v>0.91982464</v>
+        <v>0.9313224480000001</v>
       </c>
       <c r="N82">
-        <v>-0.43182464</v>
+        <v>-0.4433224480000001</v>
       </c>
       <c r="O82">
-        <v>-0.08636492800000001</v>
+        <v>-0.08866448960000002</v>
       </c>
       <c r="P82">
-        <v>-0.345459712</v>
+        <v>-0.3546579584000001</v>
       </c>
       <c r="Q82">
-        <v>-0.259459712</v>
+        <v>-0.2686579584000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3472346369777314</v>
+        <v>0.3630996178712963</v>
       </c>
       <c r="T82">
-        <v>4.663097966343133</v>
+        <v>4.908524175098036</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1061071814731991</v>
+        <v>0.1047972162698262</v>
       </c>
       <c r="W82">
-        <v>0.1794936779601816</v>
+        <v>0.1797567189730189</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5305359073659953</v>
+        <v>0.523986081349131</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8176,22 +8176,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2145918697636916</v>
+        <v>0.2161418697636916</v>
       </c>
       <c r="C83">
-        <v>-0.2326850795197908</v>
+        <v>-0.2976374403501731</v>
       </c>
       <c r="D83">
-        <v>0.8453749204802098</v>
+        <v>0.8376825596498273</v>
       </c>
       <c r="E83">
-        <v>4.57206</v>
+        <v>4.629320000000001</v>
       </c>
       <c r="F83">
-        <v>4.63806</v>
+        <v>4.695320000000001</v>
       </c>
       <c r="G83">
         <v>3.56</v>
@@ -8212,37 +8212,37 @@
         <v>0.488</v>
       </c>
       <c r="M83">
-        <v>0.9313224480000001</v>
+        <v>0.9428202560000002</v>
       </c>
       <c r="N83">
-        <v>-0.4433224480000001</v>
+        <v>-0.4548202560000002</v>
       </c>
       <c r="O83">
-        <v>-0.08866448960000002</v>
+        <v>-0.09096405120000005</v>
       </c>
       <c r="P83">
-        <v>-0.3546579584000001</v>
+        <v>-0.3638562048000001</v>
       </c>
       <c r="Q83">
-        <v>-0.2686579584000001</v>
+        <v>-0.2778562048000002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3630996178712963</v>
+        <v>0.3807273744197017</v>
       </c>
       <c r="T83">
-        <v>4.908524175098036</v>
+        <v>5.181219962603482</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1047972162698262</v>
+        <v>0.1035192014372674</v>
       </c>
       <c r="W83">
-        <v>0.1797567189730189</v>
+        <v>0.1800133443513967</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.523986081349131</v>
+        <v>0.5175960071863368</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8258,22 +8258,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2161418697636916</v>
+        <v>0.2176918697636916</v>
       </c>
       <c r="C84">
-        <v>-0.2976374403501731</v>
+        <v>-0.3624510725797965</v>
       </c>
       <c r="D84">
-        <v>0.8376825596498273</v>
+        <v>0.8301289274202039</v>
       </c>
       <c r="E84">
-        <v>4.629320000000001</v>
+        <v>4.68658</v>
       </c>
       <c r="F84">
-        <v>4.695320000000001</v>
+        <v>4.75258</v>
       </c>
       <c r="G84">
         <v>3.56</v>
@@ -8294,37 +8294,37 @@
         <v>0.488</v>
       </c>
       <c r="M84">
-        <v>0.9428202560000002</v>
+        <v>0.9543180640000001</v>
       </c>
       <c r="N84">
-        <v>-0.4548202560000002</v>
+        <v>-0.4663180640000001</v>
       </c>
       <c r="O84">
-        <v>-0.09096405120000005</v>
+        <v>-0.09326361280000002</v>
       </c>
       <c r="P84">
-        <v>-0.3638562048000001</v>
+        <v>-0.3730544512000001</v>
       </c>
       <c r="Q84">
-        <v>-0.2778562048000002</v>
+        <v>-0.2870544512000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3807273744197017</v>
+        <v>0.4004289846796841</v>
       </c>
       <c r="T84">
-        <v>5.181219962603482</v>
+        <v>5.485997607462511</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1035192014372674</v>
+        <v>0.1022719821428425</v>
       </c>
       <c r="W84">
-        <v>0.1800133443513967</v>
+        <v>0.1802637859857172</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5175960071863368</v>
+        <v>0.5113599107142124</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8340,22 +8340,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2176918697636916</v>
+        <v>0.2192418697636916</v>
       </c>
       <c r="C85">
-        <v>-0.3624510725797965</v>
+        <v>-0.4271296955412209</v>
       </c>
       <c r="D85">
-        <v>0.8301289274202039</v>
+        <v>0.8227103044587796</v>
       </c>
       <c r="E85">
-        <v>4.68658</v>
+        <v>4.743840000000001</v>
       </c>
       <c r="F85">
-        <v>4.75258</v>
+        <v>4.80984</v>
       </c>
       <c r="G85">
         <v>3.56</v>
@@ -8376,37 +8376,37 @@
         <v>0.488</v>
       </c>
       <c r="M85">
-        <v>0.9543180640000001</v>
+        <v>0.9658158720000001</v>
       </c>
       <c r="N85">
-        <v>-0.4663180640000001</v>
+        <v>-0.4778158720000001</v>
       </c>
       <c r="O85">
-        <v>-0.09326361280000002</v>
+        <v>-0.09556317440000002</v>
       </c>
       <c r="P85">
-        <v>-0.3730544512000001</v>
+        <v>-0.3822526976000001</v>
       </c>
       <c r="Q85">
-        <v>-0.2870544512000001</v>
+        <v>-0.2962526976000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4004289846796841</v>
+        <v>0.4225932962221645</v>
       </c>
       <c r="T85">
-        <v>5.485997607462511</v>
+        <v>5.828872457928918</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1022719821428425</v>
+        <v>0.1010544585459039</v>
       </c>
       <c r="W85">
-        <v>0.1802637859857172</v>
+        <v>0.1805082647239825</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5113599107142124</v>
+        <v>0.5052722927295192</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8422,22 +8422,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2192418697636916</v>
+        <v>0.2513719247038748</v>
       </c>
       <c r="C86">
-        <v>-0.42712969554122</v>
+        <v>-0.6129759668435542</v>
       </c>
       <c r="D86">
-        <v>0.8227103044587796</v>
+        <v>0.6941240331564457</v>
       </c>
       <c r="E86">
-        <v>4.74384</v>
+        <v>4.8011</v>
       </c>
       <c r="F86">
-        <v>4.809839999999999</v>
+        <v>4.8671</v>
       </c>
       <c r="G86">
         <v>3.56</v>
@@ -8458,45 +8458,45 @@
         <v>0.488</v>
       </c>
       <c r="M86">
-        <v>0.965815872</v>
+        <v>1.14766218</v>
       </c>
       <c r="N86">
-        <v>-0.477815872</v>
+        <v>-0.65966218</v>
       </c>
       <c r="O86">
-        <v>-0.09556317440000001</v>
+        <v>-0.131932436</v>
       </c>
       <c r="P86">
-        <v>-0.3822526976</v>
+        <v>-0.5277297439999999</v>
       </c>
       <c r="Q86">
-        <v>-0.2962526976</v>
+        <v>-0.441729744</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4225932962221642</v>
+        <v>0.4532465489048629</v>
       </c>
       <c r="T86">
-        <v>5.828872457928915</v>
+        <v>6.303068528027701</v>
       </c>
       <c r="U86">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.1010544585459039</v>
+        <v>0.08504244689844184</v>
       </c>
       <c r="W86">
-        <v>0.1805082647239825</v>
+        <v>0.2157469910213474</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y86">
-        <v>0.5052722927295193</v>
+        <v>0.4252122344922092</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8504,22 +8504,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2513719247038748</v>
+        <v>0.2532719247038748</v>
       </c>
       <c r="C87">
-        <v>-0.6129759668435542</v>
+        <v>-0.6765926614415321</v>
       </c>
       <c r="D87">
-        <v>0.6941240331564457</v>
+        <v>0.6877673385584675</v>
       </c>
       <c r="E87">
-        <v>4.8011</v>
+        <v>4.85836</v>
       </c>
       <c r="F87">
-        <v>4.8671</v>
+        <v>4.92436</v>
       </c>
       <c r="G87">
         <v>3.56</v>
@@ -8540,37 +8540,37 @@
         <v>0.488</v>
       </c>
       <c r="M87">
-        <v>1.14766218</v>
+        <v>1.161164088</v>
       </c>
       <c r="N87">
-        <v>-0.65966218</v>
+        <v>-0.673164088</v>
       </c>
       <c r="O87">
-        <v>-0.131932436</v>
+        <v>-0.1346328176</v>
       </c>
       <c r="P87">
-        <v>-0.5277297439999999</v>
+        <v>-0.5385312704</v>
       </c>
       <c r="Q87">
-        <v>-0.441729744</v>
+        <v>-0.4525312704000001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4532465489048629</v>
+        <v>0.482349873826639</v>
       </c>
       <c r="T87">
-        <v>6.303068528027701</v>
+        <v>6.75328770860111</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.08504244689844184</v>
+        <v>0.08405358123683204</v>
       </c>
       <c r="W87">
-        <v>0.2157469910213474</v>
+        <v>0.215980165544355</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4252122344922092</v>
+        <v>0.4202679061841602</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8586,22 +8586,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2532719247038748</v>
+        <v>0.2551719247038747</v>
       </c>
       <c r="C88">
-        <v>-0.6765926614415321</v>
+        <v>-0.7400939850817929</v>
       </c>
       <c r="D88">
-        <v>0.6877673385584675</v>
+        <v>0.6815260149182072</v>
       </c>
       <c r="E88">
-        <v>4.85836</v>
+        <v>4.915620000000001</v>
       </c>
       <c r="F88">
-        <v>4.92436</v>
+        <v>4.98162</v>
       </c>
       <c r="G88">
         <v>3.56</v>
@@ -8622,37 +8622,37 @@
         <v>0.488</v>
       </c>
       <c r="M88">
-        <v>1.161164088</v>
+        <v>1.174665996</v>
       </c>
       <c r="N88">
-        <v>-0.673164088</v>
+        <v>-0.6866659960000001</v>
       </c>
       <c r="O88">
-        <v>-0.1346328176</v>
+        <v>-0.1373331992</v>
       </c>
       <c r="P88">
-        <v>-0.5385312704</v>
+        <v>-0.5493327968000001</v>
       </c>
       <c r="Q88">
-        <v>-0.4525312704000001</v>
+        <v>-0.4633327968000002</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.482349873826639</v>
+        <v>0.5159306333517649</v>
       </c>
       <c r="T88">
-        <v>6.75328770860111</v>
+        <v>7.272771378493502</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.08405358123683204</v>
+        <v>0.08308744811916731</v>
       </c>
       <c r="W88">
-        <v>0.215980165544355</v>
+        <v>0.2162079797335003</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4202679061841602</v>
+        <v>0.4154372405958365</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8668,22 +8668,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2551719247038747</v>
+        <v>0.2570719247038748</v>
       </c>
       <c r="C89">
-        <v>-0.7400939850817929</v>
+        <v>-0.8034830504091408</v>
       </c>
       <c r="D89">
-        <v>0.6815260149182072</v>
+        <v>0.6753969495908591</v>
       </c>
       <c r="E89">
-        <v>4.915620000000001</v>
+        <v>4.97288</v>
       </c>
       <c r="F89">
-        <v>4.98162</v>
+        <v>5.03888</v>
       </c>
       <c r="G89">
         <v>3.56</v>
@@ -8704,37 +8704,37 @@
         <v>0.488</v>
       </c>
       <c r="M89">
-        <v>1.174665996</v>
+        <v>1.188167904</v>
       </c>
       <c r="N89">
-        <v>-0.6866659960000001</v>
+        <v>-0.700167904</v>
       </c>
       <c r="O89">
-        <v>-0.1373331992</v>
+        <v>-0.1400335808</v>
       </c>
       <c r="P89">
-        <v>-0.5493327968000001</v>
+        <v>-0.5601343232</v>
       </c>
       <c r="Q89">
-        <v>-0.4633327968000002</v>
+        <v>-0.4741343232</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5159306333517649</v>
+        <v>0.5551081861310788</v>
       </c>
       <c r="T89">
-        <v>7.272771378493502</v>
+        <v>7.878835660034629</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.08308744811916731</v>
+        <v>0.08214327257235859</v>
       </c>
       <c r="W89">
-        <v>0.2162079797335003</v>
+        <v>0.2164306163274379</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4154372405958365</v>
+        <v>0.410716362861793</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8750,22 +8750,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2570719247038748</v>
+        <v>0.2589719247038748</v>
       </c>
       <c r="C90">
-        <v>-0.8034830504091408</v>
+        <v>-0.8667628590964496</v>
       </c>
       <c r="D90">
-        <v>0.6753969495908591</v>
+        <v>0.6693771409035508</v>
       </c>
       <c r="E90">
-        <v>4.97288</v>
+        <v>5.03014</v>
       </c>
       <c r="F90">
-        <v>5.03888</v>
+        <v>5.09614</v>
       </c>
       <c r="G90">
         <v>3.56</v>
@@ -8786,37 +8786,37 @@
         <v>0.488</v>
       </c>
       <c r="M90">
-        <v>1.188167904</v>
+        <v>1.201669812</v>
       </c>
       <c r="N90">
-        <v>-0.700167904</v>
+        <v>-0.713669812</v>
       </c>
       <c r="O90">
-        <v>-0.1400335808</v>
+        <v>-0.1427339624</v>
       </c>
       <c r="P90">
-        <v>-0.5601343232</v>
+        <v>-0.5709358496</v>
       </c>
       <c r="Q90">
-        <v>-0.4741343232</v>
+        <v>-0.4849358496</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5551081861310788</v>
+        <v>0.6014089303248132</v>
       </c>
       <c r="T90">
-        <v>7.878835660034629</v>
+        <v>8.595093447310505</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.08214327257235859</v>
+        <v>0.08122031445356805</v>
       </c>
       <c r="W90">
-        <v>0.2164306163274379</v>
+        <v>0.2166482498518487</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.410716362861793</v>
+        <v>0.4061015722678403</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8832,22 +8832,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2589719247038748</v>
+        <v>0.2608719247038747</v>
       </c>
       <c r="C91">
-        <v>-0.8667628590964496</v>
+        <v>-0.9299363067464288</v>
       </c>
       <c r="D91">
-        <v>0.6693771409035508</v>
+        <v>0.6634636932535712</v>
       </c>
       <c r="E91">
-        <v>5.03014</v>
+        <v>5.087400000000001</v>
       </c>
       <c r="F91">
-        <v>5.09614</v>
+        <v>5.1534</v>
       </c>
       <c r="G91">
         <v>3.56</v>
@@ -8868,37 +8868,37 @@
         <v>0.488</v>
       </c>
       <c r="M91">
-        <v>1.201669812</v>
+        <v>1.21517172</v>
       </c>
       <c r="N91">
-        <v>-0.713669812</v>
+        <v>-0.7271717200000001</v>
       </c>
       <c r="O91">
-        <v>-0.1427339624</v>
+        <v>-0.145434344</v>
       </c>
       <c r="P91">
-        <v>-0.5709358496</v>
+        <v>-0.5817373760000001</v>
       </c>
       <c r="Q91">
-        <v>-0.4849358496</v>
+        <v>-0.4957373760000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6014089303248132</v>
+        <v>0.6569698233572946</v>
       </c>
       <c r="T91">
-        <v>8.595093447310505</v>
+        <v>9.454602792041555</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.08122031445356805</v>
+        <v>0.08031786651519507</v>
       </c>
       <c r="W91">
-        <v>0.2166482498518487</v>
+        <v>0.216861047075717</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4061015722678403</v>
+        <v>0.4015893325759753</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8914,22 +8914,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2608719247038747</v>
+        <v>0.2627719247038748</v>
       </c>
       <c r="C92">
-        <v>-0.9299363067464288</v>
+        <v>-0.9930061875358547</v>
       </c>
       <c r="D92">
-        <v>0.6634636932535712</v>
+        <v>0.6576538124641452</v>
       </c>
       <c r="E92">
-        <v>5.087400000000001</v>
+        <v>5.14466</v>
       </c>
       <c r="F92">
-        <v>5.1534</v>
+        <v>5.21066</v>
       </c>
       <c r="G92">
         <v>3.56</v>
@@ -8950,37 +8950,37 @@
         <v>0.488</v>
       </c>
       <c r="M92">
-        <v>1.21517172</v>
+        <v>1.228673628</v>
       </c>
       <c r="N92">
-        <v>-0.7271717200000001</v>
+        <v>-0.7406736279999999</v>
       </c>
       <c r="O92">
-        <v>-0.145434344</v>
+        <v>-0.1481347256</v>
       </c>
       <c r="P92">
-        <v>-0.5817373760000001</v>
+        <v>-0.5925389024</v>
       </c>
       <c r="Q92">
-        <v>-0.4957373760000001</v>
+        <v>-0.5065389024</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6569698233572946</v>
+        <v>0.7248775815081052</v>
       </c>
       <c r="T92">
-        <v>9.454602792041555</v>
+        <v>10.50511421337951</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.08031786651519507</v>
+        <v>0.07943525259744569</v>
       </c>
       <c r="W92">
-        <v>0.216861047075717</v>
+        <v>0.2170691674375223</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.4015893325759753</v>
+        <v>0.3971762629872284</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8996,22 +8996,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2627719247038748</v>
+        <v>0.2646719247038748</v>
       </c>
       <c r="C93">
-        <v>-0.9930061875358547</v>
+        <v>-1.055975198617896</v>
       </c>
       <c r="D93">
-        <v>0.6576538124641452</v>
+        <v>0.651944801382105</v>
       </c>
       <c r="E93">
-        <v>5.14466</v>
+        <v>5.20192</v>
       </c>
       <c r="F93">
-        <v>5.21066</v>
+        <v>5.26792</v>
       </c>
       <c r="G93">
         <v>3.56</v>
@@ -9032,37 +9032,37 @@
         <v>0.488</v>
       </c>
       <c r="M93">
-        <v>1.228673628</v>
+        <v>1.242175536</v>
       </c>
       <c r="N93">
-        <v>-0.7406736279999999</v>
+        <v>-0.7541755360000002</v>
       </c>
       <c r="O93">
-        <v>-0.1481347256</v>
+        <v>-0.1508351072</v>
       </c>
       <c r="P93">
-        <v>-0.5925389024</v>
+        <v>-0.6033404288000002</v>
       </c>
       <c r="Q93">
-        <v>-0.5065389024</v>
+        <v>-0.5173404288000002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7248775815081052</v>
+        <v>0.8097622791966185</v>
       </c>
       <c r="T93">
-        <v>10.50511421337951</v>
+        <v>11.81825349005195</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.07943525259744569</v>
+        <v>0.07857182593877778</v>
       </c>
       <c r="W93">
-        <v>0.2170691674375223</v>
+        <v>0.2172727634436362</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3971762629872284</v>
+        <v>0.3928591296938888</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9078,22 +9078,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2646719247038748</v>
+        <v>0.2665719247038748</v>
       </c>
       <c r="C94">
-        <v>-1.055975198617896</v>
+        <v>-1.118845944297118</v>
       </c>
       <c r="D94">
-        <v>0.651944801382105</v>
+        <v>0.6463340557028822</v>
       </c>
       <c r="E94">
-        <v>5.20192</v>
+        <v>5.259180000000001</v>
       </c>
       <c r="F94">
-        <v>5.26792</v>
+        <v>5.32518</v>
       </c>
       <c r="G94">
         <v>3.56</v>
@@ -9114,37 +9114,37 @@
         <v>0.488</v>
       </c>
       <c r="M94">
-        <v>1.242175536</v>
+        <v>1.255677444</v>
       </c>
       <c r="N94">
-        <v>-0.7541755360000002</v>
+        <v>-0.7676774440000003</v>
       </c>
       <c r="O94">
-        <v>-0.1508351072</v>
+        <v>-0.1535354888000001</v>
       </c>
       <c r="P94">
-        <v>-0.6033404288000002</v>
+        <v>-0.6141419552000003</v>
       </c>
       <c r="Q94">
-        <v>-0.5173404288000002</v>
+        <v>-0.5281419552000003</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8097622791966185</v>
+        <v>0.9188997476532784</v>
       </c>
       <c r="T94">
-        <v>11.81825349005195</v>
+        <v>13.50657541720223</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.07857182593877778</v>
+        <v>0.07772696759535005</v>
       </c>
       <c r="W94">
-        <v>0.2172727634436362</v>
+        <v>0.2174719810410165</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3928591296938888</v>
+        <v>0.3886348379767502</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9160,22 +9160,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2665719247038748</v>
+        <v>0.2684719247038748</v>
       </c>
       <c r="C95">
-        <v>-1.118845944297118</v>
+        <v>-1.181620939990753</v>
       </c>
       <c r="D95">
-        <v>0.6463340557028822</v>
+        <v>0.6408190600092464</v>
       </c>
       <c r="E95">
-        <v>5.259180000000001</v>
+        <v>5.31644</v>
       </c>
       <c r="F95">
-        <v>5.32518</v>
+        <v>5.38244</v>
       </c>
       <c r="G95">
         <v>3.56</v>
@@ -9196,37 +9196,37 @@
         <v>0.488</v>
       </c>
       <c r="M95">
-        <v>1.255677444</v>
+        <v>1.269179352</v>
       </c>
       <c r="N95">
-        <v>-0.7676774440000003</v>
+        <v>-0.7811793520000001</v>
       </c>
       <c r="O95">
-        <v>-0.1535354888000001</v>
+        <v>-0.1562358704</v>
       </c>
       <c r="P95">
-        <v>-0.6141419552000003</v>
+        <v>-0.6249434816000001</v>
       </c>
       <c r="Q95">
-        <v>-0.5281419552000003</v>
+        <v>-0.5389434816000002</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9188997476532784</v>
+        <v>1.064416372262158</v>
       </c>
       <c r="T95">
-        <v>13.50657541720223</v>
+        <v>15.75767132006927</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.07772696759535005</v>
+        <v>0.07690008496135697</v>
       </c>
       <c r="W95">
-        <v>0.2174719810410165</v>
+        <v>0.217666959966112</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3886348379767502</v>
+        <v>0.3845004248067849</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9242,22 +9242,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2684719247038748</v>
+        <v>0.2703719247038747</v>
       </c>
       <c r="C96">
-        <v>-1.181620939990753</v>
+        <v>-1.244302615988869</v>
       </c>
       <c r="D96">
-        <v>0.6408190600092464</v>
+        <v>0.6353973840111311</v>
       </c>
       <c r="E96">
-        <v>5.31644</v>
+        <v>5.3737</v>
       </c>
       <c r="F96">
-        <v>5.38244</v>
+        <v>5.4397</v>
       </c>
       <c r="G96">
         <v>3.56</v>
@@ -9278,37 +9278,37 @@
         <v>0.488</v>
       </c>
       <c r="M96">
-        <v>1.269179352</v>
+        <v>1.28268126</v>
       </c>
       <c r="N96">
-        <v>-0.7811793520000001</v>
+        <v>-0.7946812600000002</v>
       </c>
       <c r="O96">
-        <v>-0.1562358704</v>
+        <v>-0.1589362520000001</v>
       </c>
       <c r="P96">
-        <v>-0.6249434816000001</v>
+        <v>-0.6357450080000001</v>
       </c>
       <c r="Q96">
-        <v>-0.5389434816000002</v>
+        <v>-0.5497450080000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.064416372262158</v>
+        <v>1.268139646714591</v>
       </c>
       <c r="T96">
-        <v>15.75767132006927</v>
+        <v>18.90920558408313</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.07690008496135697</v>
+        <v>0.07609061038281638</v>
       </c>
       <c r="W96">
-        <v>0.217666959966112</v>
+        <v>0.2178578340717319</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3845004248067849</v>
+        <v>0.3804530519140819</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9324,22 +9324,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2703719247038747</v>
+        <v>0.2722719247038748</v>
       </c>
       <c r="C97">
-        <v>-1.244302615988869</v>
+        <v>-1.306893321025265</v>
       </c>
       <c r="D97">
-        <v>0.6353973840111311</v>
+        <v>0.6300666789747353</v>
       </c>
       <c r="E97">
-        <v>5.3737</v>
+        <v>5.430960000000001</v>
       </c>
       <c r="F97">
-        <v>5.4397</v>
+        <v>5.496960000000001</v>
       </c>
       <c r="G97">
         <v>3.56</v>
@@ -9360,37 +9360,37 @@
         <v>0.488</v>
       </c>
       <c r="M97">
-        <v>1.28268126</v>
+        <v>1.296183168</v>
       </c>
       <c r="N97">
-        <v>-0.7946812600000002</v>
+        <v>-0.8081831680000002</v>
       </c>
       <c r="O97">
-        <v>-0.1589362520000001</v>
+        <v>-0.1616366336000001</v>
       </c>
       <c r="P97">
-        <v>-0.6357450080000001</v>
+        <v>-0.6465465344000002</v>
       </c>
       <c r="Q97">
-        <v>-0.5497450080000001</v>
+        <v>-0.5605465344000002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.268139646714591</v>
+        <v>1.573724558393239</v>
       </c>
       <c r="T97">
-        <v>18.90920558408313</v>
+        <v>23.63650698010393</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.07609061038281638</v>
+        <v>0.07529799985799537</v>
       </c>
       <c r="W97">
-        <v>0.2178578340717319</v>
+        <v>0.2180447316334847</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3804530519140819</v>
+        <v>0.3764899992899768</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9406,22 +9406,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2722719247038747</v>
+        <v>0.2741719247038748</v>
       </c>
       <c r="C98">
-        <v>-1.306893321025264</v>
+        <v>-1.369395325670118</v>
       </c>
       <c r="D98">
-        <v>0.6300666789747356</v>
+        <v>0.6248246743298812</v>
       </c>
       <c r="E98">
-        <v>5.43096</v>
+        <v>5.48822</v>
       </c>
       <c r="F98">
-        <v>5.49696</v>
+        <v>5.55422</v>
       </c>
       <c r="G98">
         <v>3.56</v>
@@ -9442,37 +9442,37 @@
         <v>0.488</v>
       </c>
       <c r="M98">
-        <v>1.296183168</v>
+        <v>1.309685076</v>
       </c>
       <c r="N98">
-        <v>-0.808183168</v>
+        <v>-0.8216850760000001</v>
       </c>
       <c r="O98">
-        <v>-0.1616366336</v>
+        <v>-0.1643370152</v>
       </c>
       <c r="P98">
-        <v>-0.6465465344</v>
+        <v>-0.6573480608000001</v>
       </c>
       <c r="Q98">
-        <v>-0.5605465344</v>
+        <v>-0.5713480608000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.573724558393235</v>
+        <v>2.083032744524314</v>
       </c>
       <c r="T98">
-        <v>23.63650698010386</v>
+        <v>31.51534264013849</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.07529799985799539</v>
+        <v>0.07452173181822223</v>
       </c>
       <c r="W98">
-        <v>0.2180447316334847</v>
+        <v>0.2182277756372632</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3764899992899768</v>
+        <v>0.3726086590911111</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9488,22 +9488,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2741719247038748</v>
+        <v>0.2760719247038748</v>
       </c>
       <c r="C99">
-        <v>-1.369395325670118</v>
+        <v>-1.431810825554672</v>
       </c>
       <c r="D99">
-        <v>0.6248246743298812</v>
+        <v>0.6196691744453275</v>
       </c>
       <c r="E99">
-        <v>5.48822</v>
+        <v>5.54548</v>
       </c>
       <c r="F99">
-        <v>5.55422</v>
+        <v>5.61148</v>
       </c>
       <c r="G99">
         <v>3.56</v>
@@ -9524,37 +9524,37 @@
         <v>0.488</v>
       </c>
       <c r="M99">
-        <v>1.309685076</v>
+        <v>1.323186984</v>
       </c>
       <c r="N99">
-        <v>-0.8216850760000001</v>
+        <v>-0.8351869840000001</v>
       </c>
       <c r="O99">
-        <v>-0.1643370152</v>
+        <v>-0.1670373968</v>
       </c>
       <c r="P99">
-        <v>-0.6573480608000001</v>
+        <v>-0.6681495872000001</v>
       </c>
       <c r="Q99">
-        <v>-0.5713480608000001</v>
+        <v>-0.5821495872000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.083032744524314</v>
+        <v>3.10164911678647</v>
       </c>
       <c r="T99">
-        <v>31.51534264013849</v>
+        <v>47.27301396020773</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.07452173181822223</v>
+        <v>0.07376130598334241</v>
       </c>
       <c r="W99">
-        <v>0.2182277756372632</v>
+        <v>0.2184070840491279</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3726086590911111</v>
+        <v>0.368806529916712</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9570,22 +9570,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2760719247038748</v>
+        <v>0.2779719247038748</v>
       </c>
       <c r="C100">
-        <v>-1.431810825554672</v>
+        <v>-1.494141944437576</v>
       </c>
       <c r="D100">
-        <v>0.6196691744453275</v>
+        <v>0.6145980555624231</v>
       </c>
       <c r="E100">
-        <v>5.54548</v>
+        <v>5.60274</v>
       </c>
       <c r="F100">
-        <v>5.61148</v>
+        <v>5.66874</v>
       </c>
       <c r="G100">
         <v>3.56</v>
@@ -9606,37 +9606,37 @@
         <v>0.488</v>
       </c>
       <c r="M100">
-        <v>1.323186984</v>
+        <v>1.336688892</v>
       </c>
       <c r="N100">
-        <v>-0.8351869840000001</v>
+        <v>-0.848688892</v>
       </c>
       <c r="O100">
-        <v>-0.1670373968</v>
+        <v>-0.1697377784</v>
       </c>
       <c r="P100">
-        <v>-0.6681495872000001</v>
+        <v>-0.6789511135999999</v>
       </c>
       <c r="Q100">
-        <v>-0.5821495872000001</v>
+        <v>-0.5929511136</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.10164911678647</v>
+        <v>6.15749823357294</v>
       </c>
       <c r="T100">
-        <v>47.27301396020773</v>
+        <v>94.54602792041545</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.07376130598334241</v>
+        <v>0.07301624228654098</v>
       </c>
       <c r="W100">
-        <v>0.2184070840491279</v>
+        <v>0.2185827700688336</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9644,91 +9644,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.368806529916712</v>
+        <v>0.3650812114327049</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2779719247038748</v>
-      </c>
-      <c r="C101">
-        <v>-1.494141944437576</v>
-      </c>
-      <c r="D101">
-        <v>0.6145980555624231</v>
-      </c>
-      <c r="E101">
-        <v>5.60274</v>
-      </c>
-      <c r="F101">
-        <v>5.66874</v>
-      </c>
-      <c r="G101">
-        <v>3.56</v>
-      </c>
-      <c r="H101">
-        <v>5.66</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.574</v>
-      </c>
-      <c r="K101">
-        <v>0.08599999999999997</v>
-      </c>
-      <c r="L101">
-        <v>0.488</v>
-      </c>
-      <c r="M101">
-        <v>1.336688892</v>
-      </c>
-      <c r="N101">
-        <v>-0.848688892</v>
-      </c>
-      <c r="O101">
-        <v>-0.1697377784</v>
-      </c>
-      <c r="P101">
-        <v>-0.6789511135999999</v>
-      </c>
-      <c r="Q101">
-        <v>-0.5929511136</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.15749823357294</v>
-      </c>
-      <c r="T101">
-        <v>94.54602792041545</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.07301624228654098</v>
-      </c>
-      <c r="W101">
-        <v>0.2185827700688336</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3650812114327049</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
